--- a/testData/testData.xlsx
+++ b/testData/testData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
   <si>
     <t>testCase</t>
   </si>
@@ -43,6 +43,9 @@
   </si>
   <si>
     <t>wi</t>
+  </si>
+  <si>
+    <t>ValidCredentials</t>
   </si>
 </sst>
 </file>
@@ -360,7 +363,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
@@ -379,10 +382,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
@@ -390,12 +393,23 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>7</v>
       </c>
     </row>

--- a/testData/testData.xlsx
+++ b/testData/testData.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4507"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="login" sheetId="1" r:id="rId1"/>
+    <sheet name="opportunities" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="125725"/>
   <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
   <si>
     <t>testCase</t>
   </si>
@@ -46,6 +47,51 @@
   </si>
   <si>
     <t>ValidCredentials</t>
+  </si>
+  <si>
+    <t>Create Opportunity</t>
+  </si>
+  <si>
+    <t>OpportunityName</t>
+  </si>
+  <si>
+    <t>Tester1</t>
+  </si>
+  <si>
+    <t>AccountName</t>
+  </si>
+  <si>
+    <t>Kaos Trading Ltd</t>
+  </si>
+  <si>
+    <t>OpportunityAmount</t>
+  </si>
+  <si>
+    <t>SalesStage</t>
+  </si>
+  <si>
+    <t>Prospecting</t>
+  </si>
+  <si>
+    <t>ExpectedCloseDate</t>
+  </si>
+  <si>
+    <t>BlankMandatoryfield</t>
+  </si>
+  <si>
+    <t>InvalidAmount</t>
+  </si>
+  <si>
+    <t>Test Opportunity</t>
+  </si>
+  <si>
+    <t>abc123</t>
+  </si>
+  <si>
+    <t>AccountSearch</t>
+  </si>
+  <si>
+    <t>Kaos</t>
   </si>
 </sst>
 </file>
@@ -81,8 +127,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -355,7 +402,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -416,4 +463,103 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2">
+        <v>5000</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="1">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="1">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="1">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>
--- a/testData/testData.xlsx
+++ b/testData/testData.xlsx
@@ -1,18 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11012"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/varam/Desktop/NumpyNinja/Git_PW/Playwright_Titans/testData/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{343EA4D4-F299-6A40-82F4-9563D8878184}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="22260" windowHeight="12640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="login" sheetId="1" r:id="rId1"/>
     <sheet name="opportunities" sheetId="2" r:id="rId2"/>
+    <sheet name="LeadsData" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="125725"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -20,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="88">
   <si>
     <t>testCase</t>
   </si>
@@ -92,19 +99,240 @@
   </si>
   <si>
     <t>Kaos</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>firstName</t>
+  </si>
+  <si>
+    <t>lastName</t>
+  </si>
+  <si>
+    <t>jobTitle</t>
+  </si>
+  <si>
+    <t>department</t>
+  </si>
+  <si>
+    <t>accountName</t>
+  </si>
+  <si>
+    <t>mobile</t>
+  </si>
+  <si>
+    <t>officePhone</t>
+  </si>
+  <si>
+    <t>website</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>primaryStreet</t>
+  </si>
+  <si>
+    <t>primaryPostalcode</t>
+  </si>
+  <si>
+    <t>primaryCity</t>
+  </si>
+  <si>
+    <t>primaryState</t>
+  </si>
+  <si>
+    <t>primaryCountry</t>
+  </si>
+  <si>
+    <t>altStreet</t>
+  </si>
+  <si>
+    <t>altPostalcode</t>
+  </si>
+  <si>
+    <t>altCity</t>
+  </si>
+  <si>
+    <t>altState</t>
+  </si>
+  <si>
+    <t>altCountry</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>TC01</t>
+  </si>
+  <si>
+    <t>Mr.</t>
+  </si>
+  <si>
+    <t>Jennie</t>
+  </si>
+  <si>
+    <t>Madison</t>
+  </si>
+  <si>
+    <t>QA Engineer</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>P Piper &amp; Sons</t>
+  </si>
+  <si>
+    <t>(185) 289-4130</t>
+  </si>
+  <si>
+    <t>https://example.com</t>
+  </si>
+  <si>
+    <t>beans.hr@example.cn</t>
+  </si>
+  <si>
+    <t>123 Main Street</t>
+  </si>
+  <si>
+    <t>Texas</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>456 Second Street</t>
+  </si>
+  <si>
+    <t>Ave</t>
+  </si>
+  <si>
+    <t>Florida</t>
+  </si>
+  <si>
+    <t>Lead created for Jennie Madison</t>
+  </si>
+  <si>
+    <t>TC02</t>
+  </si>
+  <si>
+    <t>Ms.</t>
+  </si>
+  <si>
+    <t>Sarah</t>
+  </si>
+  <si>
+    <t>Johnson</t>
+  </si>
+  <si>
+    <t>Software Tester</t>
+  </si>
+  <si>
+    <t>Quality Assurance</t>
+  </si>
+  <si>
+    <t>ABC Corporation</t>
+  </si>
+  <si>
+    <t>(185) 289-4131</t>
+  </si>
+  <si>
+    <t>https://example.org</t>
+  </si>
+  <si>
+    <t>sarah.johnson@example.com</t>
+  </si>
+  <si>
+    <t>10 MG Road</t>
+  </si>
+  <si>
+    <t>20 Park Street</t>
+  </si>
+  <si>
+    <t>Test lead for Sarah Johnson</t>
+  </si>
+  <si>
+    <t>TC03</t>
+  </si>
+  <si>
+    <t>Dr.</t>
+  </si>
+  <si>
+    <t>Robert</t>
+  </si>
+  <si>
+    <t>Smith</t>
+  </si>
+  <si>
+    <t>Project Manager</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>XYZ Technologies</t>
+  </si>
+  <si>
+    <t>(185) 289-4132</t>
+  </si>
+  <si>
+    <t>https://example.net</t>
+  </si>
+  <si>
+    <t>robert.smith@example.com</t>
+  </si>
+  <si>
+    <t>25 Main Road</t>
+  </si>
+  <si>
+    <t>30 Lake Road</t>
+  </si>
+  <si>
+    <t>Test lead for Robert Smith</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FF0066CC"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF333333"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -127,9 +355,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -402,21 +634,21 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -427,7 +659,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -438,7 +670,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -449,7 +681,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -466,18 +698,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -497,7 +729,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -517,12 +749,12 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -542,7 +774,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -550,7 +782,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -562,4 +794,286 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB7CBB58-CC32-3442-AC7F-92AB77965A23}">
+  <dimension ref="A1:V4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="3">
+        <v>9876543210</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="M2" s="3">
+        <v>40491</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="R2" s="3">
+        <v>400002</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H3" s="3">
+        <v>9876543211</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="M3" s="3">
+        <v>40491</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="R3" s="3">
+        <v>400003</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H4" s="3">
+        <v>9876543212</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="M4" s="3">
+        <v>40491</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="R4" s="3">
+        <v>560002</v>
+      </c>
+      <c r="S4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/testData/testData.xlsx
+++ b/testData/testData.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/varam/Desktop/NumpyNinja/Git_PW/Playwright_Titans/testData/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pmano\PW_CRM\Playwright_Titans\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{343EA4D4-F299-6A40-82F4-9563D8878184}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6446C1A9-A3B8-47B6-BAC0-231D13F0B78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="22260" windowHeight="12640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="login" sheetId="1" r:id="rId1"/>
     <sheet name="opportunities" sheetId="2" r:id="rId2"/>
     <sheet name="LeadsData" sheetId="3" r:id="rId3"/>
+    <sheet name="Documents" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="125725"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="91">
   <si>
     <t>testCase</t>
   </si>
@@ -291,12 +292,24 @@
   </si>
   <si>
     <t>Test lead for Robert Smith</t>
+  </si>
+  <si>
+    <t>PUBLISH DATE</t>
+  </si>
+  <si>
+    <t>REVISION</t>
+  </si>
+  <si>
+    <t>TC001</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd;@"/>
+  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -355,13 +368,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -643,12 +657,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -659,7 +673,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -670,7 +684,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -681,7 +695,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -700,16 +714,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -729,7 +743,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -749,12 +763,12 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -774,7 +788,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -782,7 +796,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -799,9 +813,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB7CBB58-CC32-3442-AC7F-92AB77965A23}">
   <dimension ref="A1:V4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -869,7 +883,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>45</v>
       </c>
@@ -937,7 +951,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>62</v>
       </c>
@@ -1005,7 +1019,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>75</v>
       </c>
@@ -1071,6 +1085,60 @@
       </c>
       <c r="V4" s="3" t="s">
         <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01E85675-CCBB-4BF0-940B-9BD2D2BEEE01}">
+  <dimension ref="A1:U2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" s="6">
+        <v>47026</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/testData/testData.xlsx
+++ b/testData/testData.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pmano\PW_CRM\Playwright_Titans\testData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/varam/Desktop/NumpyNinja/Git_PW/Playwright_Titans/testData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6446C1A9-A3B8-47B6-BAC0-231D13F0B78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{343EA4D4-F299-6A40-82F4-9563D8878184}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="22260" windowHeight="12640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="login" sheetId="1" r:id="rId1"/>
     <sheet name="opportunities" sheetId="2" r:id="rId2"/>
     <sheet name="LeadsData" sheetId="3" r:id="rId3"/>
-    <sheet name="Documents" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="125725"/>
   <extLst>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="88">
   <si>
     <t>testCase</t>
   </si>
@@ -292,24 +291,12 @@
   </si>
   <si>
     <t>Test lead for Robert Smith</t>
-  </si>
-  <si>
-    <t>PUBLISH DATE</t>
-  </si>
-  <si>
-    <t>REVISION</t>
-  </si>
-  <si>
-    <t>TC001</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd;@"/>
-  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -368,14 +355,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -657,12 +643,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -673,7 +659,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -684,7 +670,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -695,7 +681,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -714,16 +700,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -743,7 +729,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -763,12 +749,12 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -788,7 +774,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -796,7 +782,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -813,9 +799,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB7CBB58-CC32-3442-AC7F-92AB77965A23}">
   <dimension ref="A1:V4"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:22" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -883,7 +869,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22" ht="18" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>45</v>
       </c>
@@ -951,7 +937,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22" ht="18" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>62</v>
       </c>
@@ -1019,7 +1005,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:22" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" ht="18" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>75</v>
       </c>
@@ -1085,60 +1071,6 @@
       </c>
       <c r="V4" s="3" t="s">
         <v>87</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01E85675-CCBB-4BF0-940B-9BD2D2BEEE01}">
-  <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.90625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:21" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B2" s="6">
-        <v>47026</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/testData/testData.xlsx
+++ b/testData/testData.xlsx
@@ -1,33 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/varam/Desktop/NumpyNinja/Git_PW/Playwright_Titans/testData/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manga\PW1_Titans\Playwright_Titans\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{343EA4D4-F299-6A40-82F4-9563D8878184}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A8CC1B-7FAE-4580-8637-F4A155A69636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="22260" windowHeight="12640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9450" yWindow="0" windowWidth="15795" windowHeight="15030" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="login" sheetId="1" r:id="rId1"/>
     <sheet name="opportunities" sheetId="2" r:id="rId2"/>
     <sheet name="LeadsData" sheetId="3" r:id="rId3"/>
+    <sheet name="meetings" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="125725"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="91">
   <si>
     <t>testCase</t>
   </si>
@@ -291,6 +295,15 @@
   </si>
   <si>
     <t>Test lead for Robert Smith</t>
+  </si>
+  <si>
+    <t>Subject</t>
+  </si>
+  <si>
+    <t>CreateMeeting</t>
+  </si>
+  <si>
+    <t>Contract renewal1</t>
   </si>
 </sst>
 </file>
@@ -643,12 +656,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -659,7 +672,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -670,7 +683,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -681,7 +694,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -700,16 +713,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -729,7 +742,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -749,12 +762,12 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -774,7 +787,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -782,7 +795,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -799,9 +812,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB7CBB58-CC32-3442-AC7F-92AB77965A23}">
   <dimension ref="A1:V4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -869,7 +882,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" ht="18" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>45</v>
       </c>
@@ -937,7 +950,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>62</v>
       </c>
@@ -1005,7 +1018,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>75</v>
       </c>
@@ -1071,6 +1084,36 @@
       </c>
       <c r="V4" s="3" t="s">
         <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A1278E-4E8F-4C4D-B5F7-52E9C6CC17A7}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/testData/testData.xlsx
+++ b/testData/testData.xlsx
@@ -306,7 +306,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -316,7 +316,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -344,6 +344,12 @@
       <sz val="14"/>
       <color rgb="FF333333"/>
       <name val="Helvetica"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -374,7 +380,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -415,14 +421,20 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -800,9 +812,9 @@
     <col min="1" max="1" style="6" width="27.005" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="6" width="17.433571428571426" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="6" width="15.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="17" width="19.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="19" width="19.290714285714284" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="18" width="10.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="20" width="10.719285714285713" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -815,13 +827,13 @@
       <c r="C1" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="15" t="s">
         <v>73</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="16" t="s">
         <v>75</v>
       </c>
     </row>
@@ -841,7 +853,7 @@
       <c r="E2" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="F2" s="16">
+      <c r="F2" s="17">
         <v>46387</v>
       </c>
     </row>
@@ -851,9 +863,9 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
-      <c r="D3" s="14"/>
+      <c r="D3" s="18"/>
       <c r="E3" s="4"/>
-      <c r="F3" s="15"/>
+      <c r="F3" s="16"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="4" t="s">
@@ -865,13 +877,13 @@
       <c r="C4" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="15" t="s">
         <v>83</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="F4" s="16">
+      <c r="F4" s="17">
         <v>46387</v>
       </c>
     </row>
@@ -881,9 +893,9 @@
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
-      <c r="D5" s="14"/>
+      <c r="D5" s="18"/>
       <c r="E5" s="4"/>
-      <c r="F5" s="16">
+      <c r="F5" s="17">
         <v>46387</v>
       </c>
     </row>
@@ -895,9 +907,9 @@
       <c r="C6" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D6" s="14"/>
+      <c r="D6" s="18"/>
       <c r="E6" s="4"/>
-      <c r="F6" s="15"/>
+      <c r="F6" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -912,28 +924,28 @@
   <dimension ref="A1:V4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="13" max="13" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="18" max="18" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -1227,7 +1239,7 @@
     <col min="4" max="4" style="7" width="20.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1241,7 +1253,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>

--- a/testData/testData.xlsx
+++ b/testData/testData.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manga\PW1_Titans\Playwright_Titans\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A8CC1B-7FAE-4580-8637-F4A155A69636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{149CB0A3-319D-4906-A129-6365F197BDC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9450" yWindow="0" windowWidth="15795" windowHeight="15030" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10800" yWindow="210" windowWidth="15795" windowHeight="15030" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="login" sheetId="1" r:id="rId1"/>
     <sheet name="opportunities" sheetId="2" r:id="rId2"/>
     <sheet name="LeadsData" sheetId="3" r:id="rId3"/>
     <sheet name="meetings" sheetId="4" r:id="rId4"/>
+    <sheet name="Quotes" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="125725"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="97">
   <si>
     <t>testCase</t>
   </si>
@@ -304,6 +305,24 @@
   </si>
   <si>
     <t>Contract renewal1</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>QuoteStage</t>
+  </si>
+  <si>
+    <t>ValidUntilDay</t>
+  </si>
+  <si>
+    <t>CreateQuotes</t>
+  </si>
+  <si>
+    <t>Testquotes1</t>
+  </si>
+  <si>
+    <t>On Hold</t>
   </si>
 </sst>
 </file>
@@ -1119,4 +1138,48 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3999D4B7-9BE6-4044-8ADC-BC12427306A3}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/testData/testData.xlsx
+++ b/testData/testData.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/varam/Desktop/NumpyNinja/Git_PW/Playwright_Titans/testData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{343EA4D4-F299-6A40-82F4-9563D8878184}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E4F1D9C-C565-2447-AC2C-CD3CD8F4BD30}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="22260" windowHeight="12640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="login" sheetId="1" r:id="rId1"/>
     <sheet name="opportunities" sheetId="2" r:id="rId2"/>
     <sheet name="LeadsData" sheetId="3" r:id="rId3"/>
+    <sheet name="AccountsData" sheetId="5" r:id="rId4"/>
+    <sheet name="Documents" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="125725"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="346">
   <si>
     <t>testCase</t>
   </si>
@@ -257,49 +259,840 @@
     <t>TC03</t>
   </si>
   <si>
-    <t>Dr.</t>
-  </si>
-  <si>
-    <t>Robert</t>
-  </si>
-  <si>
-    <t>Smith</t>
+    <t>PUBLISH DATE</t>
+  </si>
+  <si>
+    <t>REVISION</t>
+  </si>
+  <si>
+    <t>TC001</t>
+  </si>
+  <si>
+    <t>TC04</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>emailAddress</t>
+  </si>
+  <si>
+    <t>billingStreet</t>
+  </si>
+  <si>
+    <t>billingPostalcode</t>
+  </si>
+  <si>
+    <t>billingCity</t>
+  </si>
+  <si>
+    <t>billingState</t>
+  </si>
+  <si>
+    <t>billingCountry</t>
+  </si>
+  <si>
+    <t>shippingStreet</t>
+  </si>
+  <si>
+    <t>shippingPostalcode</t>
+  </si>
+  <si>
+    <t>shippingCity</t>
+  </si>
+  <si>
+    <t>shippingState</t>
+  </si>
+  <si>
+    <t>shippingCountry</t>
+  </si>
+  <si>
+    <t>Acme Solutions</t>
+  </si>
+  <si>
+    <t>https://www.acmesolutions.com</t>
+  </si>
+  <si>
+    <t>contact@acmesolutions.com</t>
+  </si>
+  <si>
+    <t>100 Main Street</t>
+  </si>
+  <si>
+    <t>200 Market Street</t>
+  </si>
+  <si>
+    <t>Mandatory account test data</t>
+  </si>
+  <si>
+    <t>Global Tech Services</t>
+  </si>
+  <si>
+    <t>https://www.globaltechservices.com</t>
+  </si>
+  <si>
+    <t>info@globaltechservices.com</t>
+  </si>
+  <si>
+    <t>Complete account test data</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>500 Michigan Avenue</t>
+  </si>
+  <si>
+    <t>Chicago</t>
+  </si>
+  <si>
+    <t>Illinois</t>
+  </si>
+  <si>
+    <t>700 W Madison Street</t>
+  </si>
+  <si>
+    <t>San Francisco</t>
+  </si>
+  <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>https://www.bluehorizon.example</t>
+  </si>
+  <si>
+    <t>contact@bluehorizon.example</t>
+  </si>
+  <si>
+    <t>120 Biscayne Boulevard</t>
+  </si>
+  <si>
+    <t>Miami</t>
+  </si>
+  <si>
+    <t>250 Brickell Avenue</t>
+  </si>
+  <si>
+    <t>Media account test data</t>
+  </si>
+  <si>
+    <t>TC05</t>
+  </si>
+  <si>
+    <t>Silver Oak Industries</t>
+  </si>
+  <si>
+    <t>https://www.silveroak.example</t>
+  </si>
+  <si>
+    <t>sales@silveroak.example</t>
+  </si>
+  <si>
+    <t>1800 Main Street</t>
+  </si>
+  <si>
+    <t>Dallas</t>
+  </si>
+  <si>
+    <t>2200 Ross Avenue</t>
+  </si>
+  <si>
+    <t>Industrial account test data</t>
+  </si>
+  <si>
+    <t>TC06</t>
+  </si>
+  <si>
+    <t>Green Valley Foods</t>
+  </si>
+  <si>
+    <t>https://www.greenvalley.example</t>
+  </si>
+  <si>
+    <t>orders@greenvalley.example</t>
+  </si>
+  <si>
+    <t>800 Pine Street</t>
+  </si>
+  <si>
+    <t>Seattle</t>
+  </si>
+  <si>
+    <t>Washington</t>
+  </si>
+  <si>
+    <t>1200 5th Avenue</t>
+  </si>
+  <si>
+    <t>Food industry account test data</t>
+  </si>
+  <si>
+    <t>TC07</t>
+  </si>
+  <si>
+    <t>Summit Peak Software</t>
+  </si>
+  <si>
+    <t>https://www.summitpeak.example</t>
+  </si>
+  <si>
+    <t>support@summitpeak.example</t>
+  </si>
+  <si>
+    <t>1600 Broadway</t>
+  </si>
+  <si>
+    <t>Denver</t>
+  </si>
+  <si>
+    <t>Colorado</t>
+  </si>
+  <si>
+    <t>1700 Lincoln Street</t>
+  </si>
+  <si>
+    <t>Software account test data</t>
+  </si>
+  <si>
+    <t>TC08</t>
+  </si>
+  <si>
+    <t>Golden Gate Logistics</t>
+  </si>
+  <si>
+    <t>https://www.goldengate.example</t>
+  </si>
+  <si>
+    <t>logistics@goldengate.example</t>
+  </si>
+  <si>
+    <t>700 Airport Boulevard</t>
+  </si>
+  <si>
+    <t>San Jose</t>
+  </si>
+  <si>
+    <t>900 Coleman Avenue</t>
+  </si>
+  <si>
+    <t>Logistics account test data</t>
+  </si>
+  <si>
+    <t>TC09</t>
+  </si>
+  <si>
+    <t>Liberty Financial Group</t>
+  </si>
+  <si>
+    <t>https://www.libertyfinancial.example</t>
+  </si>
+  <si>
+    <t>finance@libertyfinancial.example</t>
+  </si>
+  <si>
+    <t>200 Clarendon Street</t>
+  </si>
+  <si>
+    <t>Boston</t>
+  </si>
+  <si>
+    <t>Massachusetts</t>
+  </si>
+  <si>
+    <t>100 Federal Street</t>
+  </si>
+  <si>
+    <t>Financial account test data</t>
+  </si>
+  <si>
+    <t>TC10</t>
+  </si>
+  <si>
+    <t>Riverstone Healthcare</t>
+  </si>
+  <si>
+    <t>https://www.riverstone.example</t>
+  </si>
+  <si>
+    <t>contact@riverstone.example</t>
+  </si>
+  <si>
+    <t>100 Peachtree Street</t>
+  </si>
+  <si>
+    <t>Atlanta</t>
+  </si>
+  <si>
+    <t>Georgia</t>
+  </si>
+  <si>
+    <t>250 Spring Street</t>
+  </si>
+  <si>
+    <t>Healthcare account test data</t>
+  </si>
+  <si>
+    <t>TC11</t>
+  </si>
+  <si>
+    <t>Pacific Edge Retail</t>
+  </si>
+  <si>
+    <t>https://www.pacificedge.example</t>
+  </si>
+  <si>
+    <t>sales@pacificedge.example</t>
+  </si>
+  <si>
+    <t>900 SW 5th Avenue</t>
+  </si>
+  <si>
+    <t>Portland</t>
+  </si>
+  <si>
+    <t>Oregon</t>
+  </si>
+  <si>
+    <t>1100 NW Everett Street</t>
+  </si>
+  <si>
+    <t>Retail account test data</t>
+  </si>
+  <si>
+    <t>TC12</t>
+  </si>
+  <si>
+    <t>Capital Bridge Partners</t>
+  </si>
+  <si>
+    <t>https://www.capitalbridge.example</t>
+  </si>
+  <si>
+    <t>info@capitalbridge.example</t>
+  </si>
+  <si>
+    <t>1200 New York Avenue NW</t>
+  </si>
+  <si>
+    <t>District of Columbia</t>
+  </si>
+  <si>
+    <t>800 Connecticut Avenue NW</t>
+  </si>
+  <si>
+    <t>Partnership account test data</t>
+  </si>
+  <si>
+    <t>Michael</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>michael.anderson@example.com</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>Account Executive</t>
+  </si>
+  <si>
+    <t>Human Resources</t>
+  </si>
+  <si>
+    <t>James</t>
+  </si>
+  <si>
+    <t>Parker</t>
+  </si>
+  <si>
+    <t>Software Engineer</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>james.parker@example.com</t>
+  </si>
+  <si>
+    <t>Emma</t>
+  </si>
+  <si>
+    <t>Wilson</t>
+  </si>
+  <si>
+    <t>Operations Manager</t>
+  </si>
+  <si>
+    <t>Operations</t>
+  </si>
+  <si>
+    <t>emma.wilson@example.com</t>
+  </si>
+  <si>
+    <t>William</t>
+  </si>
+  <si>
+    <t>Harris</t>
+  </si>
+  <si>
+    <t>Financial Analyst</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>william.harris@example.com</t>
+  </si>
+  <si>
+    <t>Ava</t>
+  </si>
+  <si>
+    <t>Thompson</t>
+  </si>
+  <si>
+    <t>ava.thompson@example.com</t>
+  </si>
+  <si>
+    <t>TC13</t>
+  </si>
+  <si>
+    <t>Ethan</t>
+  </si>
+  <si>
+    <t>Robinson</t>
+  </si>
+  <si>
+    <t>ethan.robinson@example.com</t>
+  </si>
+  <si>
+    <t>TC14</t>
+  </si>
+  <si>
+    <t>Charlotte</t>
+  </si>
+  <si>
+    <t>Davis</t>
+  </si>
+  <si>
+    <t>Business Analyst</t>
+  </si>
+  <si>
+    <t>charlotte.davis@example.com</t>
+  </si>
+  <si>
+    <t>(303) 555-9012</t>
+  </si>
+  <si>
+    <t>500 Market Street</t>
+  </si>
+  <si>
+    <t>Lead created for Michael Anderson</t>
+  </si>
+  <si>
+    <t>(408) 555-7856</t>
+  </si>
+  <si>
+    <t>300 Santa Clara Street</t>
+  </si>
+  <si>
+    <t>700 Madison Avenue</t>
+  </si>
+  <si>
+    <t>Lead created for Emma Wilson</t>
+  </si>
+  <si>
+    <t>(617) 555-2468</t>
+  </si>
+  <si>
+    <t>100 Summer Street</t>
+  </si>
+  <si>
+    <t>400 Boylston Street</t>
+  </si>
+  <si>
+    <t>Lead created for William Harris</t>
+  </si>
+  <si>
+    <t>Account Manager</t>
+  </si>
+  <si>
+    <t>(404) 555-5623</t>
+  </si>
+  <si>
+    <t>550 Peachtree Street</t>
+  </si>
+  <si>
+    <t>1200 Lenox Road</t>
+  </si>
+  <si>
+    <t>Lead created for Ava Thompson</t>
+  </si>
+  <si>
+    <t>Business</t>
+  </si>
+  <si>
+    <t>(503) 555-3189</t>
+  </si>
+  <si>
+    <t>900 SW Fifth Avenue</t>
+  </si>
+  <si>
+    <t>1200 NE Broadway</t>
+  </si>
+  <si>
+    <t>Lead created for Ethan Robinson</t>
   </si>
   <si>
     <t>Project Manager</t>
   </si>
   <si>
-    <t>Engineering</t>
-  </si>
-  <si>
-    <t>XYZ Technologies</t>
-  </si>
-  <si>
-    <t>(185) 289-4132</t>
-  </si>
-  <si>
-    <t>https://example.net</t>
-  </si>
-  <si>
-    <t>robert.smith@example.com</t>
-  </si>
-  <si>
-    <t>25 Main Road</t>
-  </si>
-  <si>
-    <t>30 Lake Road</t>
-  </si>
-  <si>
-    <t>Test lead for Robert Smith</t>
+    <t>Management</t>
+  </si>
+  <si>
+    <t>(202) 555-7291</t>
+  </si>
+  <si>
+    <t>700 Pennsylvania Avenue</t>
+  </si>
+  <si>
+    <t>DC</t>
+  </si>
+  <si>
+    <t>1600 Connecticut Avenue</t>
+  </si>
+  <si>
+    <t>Lead created for Charlotte Davis</t>
+  </si>
+  <si>
+    <t>Product Manager</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>(312) 555-6134</t>
+  </si>
+  <si>
+    <t>200 W Adams Street</t>
+  </si>
+  <si>
+    <t>Lead created for James Parker</t>
+  </si>
+  <si>
+    <t>Isabella</t>
+  </si>
+  <si>
+    <t>Moore</t>
+  </si>
+  <si>
+    <t>Recruitment Specialist</t>
+  </si>
+  <si>
+    <t>(305) 555-4827</t>
+  </si>
+  <si>
+    <t>isabella.moore@example.com</t>
+  </si>
+  <si>
+    <t>100 Biscayne Boulevard</t>
+  </si>
+  <si>
+    <t>800 Brickell Avenue</t>
+  </si>
+  <si>
+    <t>Lead created for Isabella Moore</t>
+  </si>
+  <si>
+    <t>Alexander</t>
+  </si>
+  <si>
+    <t>Taylor</t>
+  </si>
+  <si>
+    <t>Technical Lead</t>
+  </si>
+  <si>
+    <t>North Star Technologies</t>
+  </si>
+  <si>
+    <t>(512) 555-7416</t>
+  </si>
+  <si>
+    <t>alexander.taylor@example.com</t>
+  </si>
+  <si>
+    <t>600 Congress Avenue</t>
+  </si>
+  <si>
+    <t>Austin</t>
+  </si>
+  <si>
+    <t>300 Colorado Street</t>
+  </si>
+  <si>
+    <t>Lead created for Alexander Taylor</t>
+  </si>
+  <si>
+    <t>Amelia</t>
+  </si>
+  <si>
+    <t>Customer Success Manager</t>
+  </si>
+  <si>
+    <t>Customer Service</t>
+  </si>
+  <si>
+    <t>River View Solutions</t>
+  </si>
+  <si>
+    <t>(615) 555-3745</t>
+  </si>
+  <si>
+    <t>amelia.johnson@example.com</t>
+  </si>
+  <si>
+    <t>200 Broadway</t>
+  </si>
+  <si>
+    <t>Nashville</t>
+  </si>
+  <si>
+    <t>Tennessee</t>
+  </si>
+  <si>
+    <t>1000 Church Street</t>
+  </si>
+  <si>
+    <t>Lead created for Amelia Johnson</t>
+  </si>
+  <si>
+    <t>TC15</t>
+  </si>
+  <si>
+    <t>Benjamin</t>
+  </si>
+  <si>
+    <t>Clark</t>
+  </si>
+  <si>
+    <t>System Administrator</t>
+  </si>
+  <si>
+    <t>Blue Ridge Systems</t>
+  </si>
+  <si>
+    <t>(704) 555-5214</t>
+  </si>
+  <si>
+    <t>benjamin.clark@example.com</t>
+  </si>
+  <si>
+    <t>400 Tryon Street</t>
+  </si>
+  <si>
+    <t>North Carolina</t>
+  </si>
+  <si>
+    <t>600 Trade Street</t>
+  </si>
+  <si>
+    <t>Lead created for Benjamin Clark</t>
+  </si>
+  <si>
+    <t>TC16</t>
+  </si>
+  <si>
+    <t>Mia</t>
+  </si>
+  <si>
+    <t>Lewis</t>
+  </si>
+  <si>
+    <t>Business Development Manager</t>
+  </si>
+  <si>
+    <t>Sunrise Enterprises</t>
+  </si>
+  <si>
+    <t>(602) 555-8352</t>
+  </si>
+  <si>
+    <t>mia.lewis@example.com</t>
+  </si>
+  <si>
+    <t>100 N Central Avenue</t>
+  </si>
+  <si>
+    <t>Phoenix</t>
+  </si>
+  <si>
+    <t>Arizona</t>
+  </si>
+  <si>
+    <t>500 E Washington Street</t>
+  </si>
+  <si>
+    <t>Lead created for Mia Lewis</t>
+  </si>
+  <si>
+    <t>TC17</t>
+  </si>
+  <si>
+    <t>Noah</t>
+  </si>
+  <si>
+    <t>Walker</t>
+  </si>
+  <si>
+    <t>Data Analyst</t>
+  </si>
+  <si>
+    <t>Analytics</t>
+  </si>
+  <si>
+    <t>West Coast Analytics</t>
+  </si>
+  <si>
+    <t>(213) 555-4186</t>
+  </si>
+  <si>
+    <t>noah.walker@example.com</t>
+  </si>
+  <si>
+    <t>800 S Spring Street</t>
+  </si>
+  <si>
+    <t>Los Angeles</t>
+  </si>
+  <si>
+    <t>1200 Wilshire Boulevard</t>
+  </si>
+  <si>
+    <t>Lead created for Noah Walker</t>
+  </si>
+  <si>
+    <t>TC18</t>
+  </si>
+  <si>
+    <t>Harper</t>
+  </si>
+  <si>
+    <t>Hall</t>
+  </si>
+  <si>
+    <t>Lakeside Consulting</t>
+  </si>
+  <si>
+    <t>(612) 555-6271</t>
+  </si>
+  <si>
+    <t>harper.hall@example.com</t>
+  </si>
+  <si>
+    <t>500 Nicollet Mall</t>
+  </si>
+  <si>
+    <t>Minneapolis</t>
+  </si>
+  <si>
+    <t>Minnesota</t>
+  </si>
+  <si>
+    <t>800 Hennepin Avenue</t>
+  </si>
+  <si>
+    <t>Lead created for Harper Hall</t>
+  </si>
+  <si>
+    <t>TC19</t>
+  </si>
+  <si>
+    <t>Lucas</t>
+  </si>
+  <si>
+    <t>Young</t>
+  </si>
+  <si>
+    <t>DevOps Engineer</t>
+  </si>
+  <si>
+    <t>Cloud Matrix Solutions</t>
+  </si>
+  <si>
+    <t>(617) 555-3915</t>
+  </si>
+  <si>
+    <t>lucas.young@example.com</t>
+  </si>
+  <si>
+    <t>125 Summer Street</t>
+  </si>
+  <si>
+    <t>300 Congress Street</t>
+  </si>
+  <si>
+    <t>Lead created for Lucas Young</t>
+  </si>
+  <si>
+    <t>TC20</t>
+  </si>
+  <si>
+    <t>Evelyn</t>
+  </si>
+  <si>
+    <t>King</t>
+  </si>
+  <si>
+    <t>Marketing Specialist</t>
+  </si>
+  <si>
+    <t>Creative Edge Media</t>
+  </si>
+  <si>
+    <t>(415) 555-2734</t>
+  </si>
+  <si>
+    <t>evelyn.king@example.com</t>
+  </si>
+  <si>
+    <t>600 California Street</t>
+  </si>
+  <si>
+    <t>900 Market Street</t>
+  </si>
+  <si>
+    <t>Lead created for Evelyn King</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+  </numFmts>
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -334,6 +1127,29 @@
       <name val="Helvetica"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -352,18 +1168,26 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -798,8 +1622,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB7CBB58-CC32-3442-AC7F-92AB77965A23}">
-  <dimension ref="A1:V4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:V21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
@@ -1006,41 +1833,41 @@
       </c>
     </row>
     <row r="4" spans="1:22" ht="18" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="7" t="s">
         <v>75</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="H4" s="3">
-        <v>9876543212</v>
+        <v>9876543210</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="M4" s="3">
         <v>40491</v>
@@ -1055,10 +1882,10 @@
         <v>57</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="R4" s="3">
-        <v>560002</v>
+        <v>400002</v>
       </c>
       <c r="S4" s="5" t="s">
         <v>59</v>
@@ -1070,7 +1897,3892 @@
         <v>57</v>
       </c>
       <c r="V4" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+      <c r="A5" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H5" s="3">
+        <v>9876543210</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="M5" s="3">
+        <v>40491</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="R5" s="3">
+        <v>400002</v>
+      </c>
+      <c r="S5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="U5" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="V5" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" t="s">
+        <v>185</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" t="s">
+        <v>193</v>
+      </c>
+      <c r="F6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" t="s">
+        <v>134</v>
+      </c>
+      <c r="H6">
+        <v>3035554521</v>
+      </c>
+      <c r="I6" t="s">
+        <v>218</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="L6" t="s">
+        <v>140</v>
+      </c>
+      <c r="M6">
+        <v>80203</v>
+      </c>
+      <c r="N6" t="s">
+        <v>138</v>
+      </c>
+      <c r="O6" t="s">
+        <v>139</v>
+      </c>
+      <c r="P6" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>219</v>
+      </c>
+      <c r="R6">
+        <v>94105</v>
+      </c>
+      <c r="S6" t="s">
+        <v>108</v>
+      </c>
+      <c r="T6" t="s">
+        <v>109</v>
+      </c>
+      <c r="U6" t="s">
+        <v>57</v>
+      </c>
+      <c r="V6" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D7" t="s">
+        <v>197</v>
+      </c>
+      <c r="E7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F7" t="s">
+        <v>199</v>
+      </c>
+      <c r="G7" t="s">
+        <v>143</v>
+      </c>
+      <c r="H7">
+        <v>4085556234</v>
+      </c>
+      <c r="I7" t="s">
+        <v>221</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="L7" t="s">
+        <v>222</v>
+      </c>
+      <c r="M7">
+        <v>95113</v>
+      </c>
+      <c r="N7" t="s">
+        <v>147</v>
+      </c>
+      <c r="O7" t="s">
+        <v>109</v>
+      </c>
+      <c r="P7" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>223</v>
+      </c>
+      <c r="R7">
+        <v>10065</v>
+      </c>
+      <c r="S7" t="s">
+        <v>102</v>
+      </c>
+      <c r="T7" t="s">
+        <v>102</v>
+      </c>
+      <c r="U7" t="s">
+        <v>57</v>
+      </c>
+      <c r="V7" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" t="s">
+        <v>201</v>
+      </c>
+      <c r="D8" t="s">
+        <v>202</v>
+      </c>
+      <c r="E8" t="s">
+        <v>203</v>
+      </c>
+      <c r="F8" t="s">
+        <v>204</v>
+      </c>
+      <c r="G8" t="s">
+        <v>151</v>
+      </c>
+      <c r="H8">
+        <v>6175558934</v>
+      </c>
+      <c r="I8" t="s">
+        <v>225</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="L8" t="s">
+        <v>226</v>
+      </c>
+      <c r="M8">
+        <v>2110</v>
+      </c>
+      <c r="N8" t="s">
+        <v>155</v>
+      </c>
+      <c r="O8" t="s">
+        <v>156</v>
+      </c>
+      <c r="P8" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>227</v>
+      </c>
+      <c r="R8">
+        <v>2215</v>
+      </c>
+      <c r="S8" t="s">
+        <v>155</v>
+      </c>
+      <c r="T8" t="s">
+        <v>156</v>
+      </c>
+      <c r="U8" t="s">
+        <v>57</v>
+      </c>
+      <c r="V8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>142</v>
+      </c>
+      <c r="B9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" t="s">
+        <v>206</v>
+      </c>
+      <c r="D9" t="s">
+        <v>207</v>
+      </c>
+      <c r="E9" t="s">
+        <v>229</v>
+      </c>
+      <c r="F9" t="s">
+        <v>186</v>
+      </c>
+      <c r="G9" t="s">
+        <v>160</v>
+      </c>
+      <c r="H9">
+        <v>4045553178</v>
+      </c>
+      <c r="I9" t="s">
+        <v>230</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="L9" t="s">
+        <v>231</v>
+      </c>
+      <c r="M9">
+        <v>30308</v>
+      </c>
+      <c r="N9" t="s">
+        <v>164</v>
+      </c>
+      <c r="O9" t="s">
+        <v>165</v>
+      </c>
+      <c r="P9" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>232</v>
+      </c>
+      <c r="R9">
+        <v>30319</v>
+      </c>
+      <c r="S9" t="s">
+        <v>164</v>
+      </c>
+      <c r="T9" t="s">
+        <v>165</v>
+      </c>
+      <c r="U9" t="s">
+        <v>57</v>
+      </c>
+      <c r="V9" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>150</v>
+      </c>
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" t="s">
+        <v>210</v>
+      </c>
+      <c r="D10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E10" t="s">
+        <v>216</v>
+      </c>
+      <c r="F10" t="s">
+        <v>234</v>
+      </c>
+      <c r="G10" t="s">
+        <v>169</v>
+      </c>
+      <c r="H10">
+        <v>5035557412</v>
+      </c>
+      <c r="I10" t="s">
+        <v>235</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="L10" t="s">
+        <v>236</v>
+      </c>
+      <c r="M10">
+        <v>97204</v>
+      </c>
+      <c r="N10" t="s">
+        <v>173</v>
+      </c>
+      <c r="O10" t="s">
+        <v>174</v>
+      </c>
+      <c r="P10" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>237</v>
+      </c>
+      <c r="R10">
+        <v>97232</v>
+      </c>
+      <c r="S10" t="s">
+        <v>173</v>
+      </c>
+      <c r="T10" t="s">
+        <v>174</v>
+      </c>
+      <c r="U10" t="s">
+        <v>57</v>
+      </c>
+      <c r="V10" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>159</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" t="s">
+        <v>214</v>
+      </c>
+      <c r="D11" t="s">
+        <v>215</v>
+      </c>
+      <c r="E11" t="s">
+        <v>239</v>
+      </c>
+      <c r="F11" t="s">
+        <v>240</v>
+      </c>
+      <c r="G11" t="s">
+        <v>178</v>
+      </c>
+      <c r="H11">
+        <v>2025556843</v>
+      </c>
+      <c r="I11" t="s">
+        <v>241</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="L11" t="s">
+        <v>242</v>
+      </c>
+      <c r="M11">
+        <v>20004</v>
+      </c>
+      <c r="N11" t="s">
+        <v>130</v>
+      </c>
+      <c r="O11" t="s">
+        <v>243</v>
+      </c>
+      <c r="P11" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>244</v>
+      </c>
+      <c r="R11">
+        <v>20009</v>
+      </c>
+      <c r="S11" t="s">
+        <v>130</v>
+      </c>
+      <c r="T11" t="s">
+        <v>243</v>
+      </c>
+      <c r="U11" t="s">
+        <v>57</v>
+      </c>
+      <c r="V11" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>168</v>
+      </c>
+      <c r="B12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" t="s">
+        <v>191</v>
+      </c>
+      <c r="D12" t="s">
+        <v>192</v>
+      </c>
+      <c r="E12" t="s">
+        <v>246</v>
+      </c>
+      <c r="F12" t="s">
+        <v>247</v>
+      </c>
+      <c r="G12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H12">
+        <v>3125554728</v>
+      </c>
+      <c r="I12" t="s">
+        <v>248</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="L12" t="s">
+        <v>249</v>
+      </c>
+      <c r="M12">
+        <v>60606</v>
+      </c>
+      <c r="N12" t="s">
+        <v>105</v>
+      </c>
+      <c r="O12" t="s">
+        <v>106</v>
+      </c>
+      <c r="P12" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>104</v>
+      </c>
+      <c r="R12">
+        <v>60611</v>
+      </c>
+      <c r="S12" t="s">
+        <v>105</v>
+      </c>
+      <c r="T12" t="s">
+        <v>106</v>
+      </c>
+      <c r="U12" t="s">
+        <v>57</v>
+      </c>
+      <c r="V12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>177</v>
+      </c>
+      <c r="B13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" t="s">
+        <v>251</v>
+      </c>
+      <c r="D13" t="s">
+        <v>252</v>
+      </c>
+      <c r="E13" t="s">
+        <v>253</v>
+      </c>
+      <c r="F13" t="s">
+        <v>190</v>
+      </c>
+      <c r="G13" t="s">
+        <v>125</v>
+      </c>
+      <c r="H13">
+        <v>3055559361</v>
+      </c>
+      <c r="I13" t="s">
+        <v>254</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="L13" t="s">
+        <v>256</v>
+      </c>
+      <c r="M13">
+        <v>33132</v>
+      </c>
+      <c r="N13" t="s">
+        <v>113</v>
+      </c>
+      <c r="O13" t="s">
+        <v>60</v>
+      </c>
+      <c r="P13" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>257</v>
+      </c>
+      <c r="R13">
+        <v>33131</v>
+      </c>
+      <c r="S13" t="s">
+        <v>113</v>
+      </c>
+      <c r="T13" t="s">
+        <v>60</v>
+      </c>
+      <c r="U13" t="s">
+        <v>57</v>
+      </c>
+      <c r="V13" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>209</v>
+      </c>
+      <c r="B14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" t="s">
+        <v>259</v>
+      </c>
+      <c r="D14" t="s">
+        <v>260</v>
+      </c>
+      <c r="E14" t="s">
+        <v>261</v>
+      </c>
+      <c r="F14" t="s">
+        <v>194</v>
+      </c>
+      <c r="G14" t="s">
+        <v>262</v>
+      </c>
+      <c r="H14">
+        <v>5125552587</v>
+      </c>
+      <c r="I14" t="s">
+        <v>263</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="L14" t="s">
+        <v>265</v>
+      </c>
+      <c r="M14">
+        <v>78701</v>
+      </c>
+      <c r="N14" t="s">
+        <v>266</v>
+      </c>
+      <c r="O14" t="s">
+        <v>56</v>
+      </c>
+      <c r="P14" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>267</v>
+      </c>
+      <c r="R14">
+        <v>78701</v>
+      </c>
+      <c r="S14" t="s">
+        <v>266</v>
+      </c>
+      <c r="T14" t="s">
+        <v>56</v>
+      </c>
+      <c r="U14" t="s">
+        <v>57</v>
+      </c>
+      <c r="V14" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>213</v>
+      </c>
+      <c r="B15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" t="s">
+        <v>269</v>
+      </c>
+      <c r="D15" t="s">
+        <v>65</v>
+      </c>
+      <c r="E15" t="s">
+        <v>270</v>
+      </c>
+      <c r="F15" t="s">
+        <v>271</v>
+      </c>
+      <c r="G15" t="s">
+        <v>272</v>
+      </c>
+      <c r="H15">
+        <v>6155558192</v>
+      </c>
+      <c r="I15" t="s">
+        <v>273</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="L15" t="s">
+        <v>275</v>
+      </c>
+      <c r="M15">
+        <v>37201</v>
+      </c>
+      <c r="N15" t="s">
+        <v>276</v>
+      </c>
+      <c r="O15" t="s">
+        <v>277</v>
+      </c>
+      <c r="P15" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>278</v>
+      </c>
+      <c r="R15">
+        <v>37203</v>
+      </c>
+      <c r="S15" t="s">
+        <v>276</v>
+      </c>
+      <c r="T15" t="s">
+        <v>277</v>
+      </c>
+      <c r="U15" t="s">
+        <v>57</v>
+      </c>
+      <c r="V15" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>280</v>
+      </c>
+      <c r="B16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" t="s">
+        <v>281</v>
+      </c>
+      <c r="D16" t="s">
+        <v>282</v>
+      </c>
+      <c r="E16" t="s">
+        <v>283</v>
+      </c>
+      <c r="F16" t="s">
+        <v>50</v>
+      </c>
+      <c r="G16" t="s">
+        <v>284</v>
+      </c>
+      <c r="H16">
+        <v>7045556381</v>
+      </c>
+      <c r="I16" t="s">
+        <v>285</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="L16" t="s">
+        <v>287</v>
+      </c>
+      <c r="M16">
+        <v>28202</v>
+      </c>
+      <c r="N16" t="s">
+        <v>214</v>
+      </c>
+      <c r="O16" t="s">
+        <v>288</v>
+      </c>
+      <c r="P16" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>289</v>
+      </c>
+      <c r="R16">
+        <v>28202</v>
+      </c>
+      <c r="S16" t="s">
+        <v>214</v>
+      </c>
+      <c r="T16" t="s">
+        <v>288</v>
+      </c>
+      <c r="U16" t="s">
+        <v>57</v>
+      </c>
+      <c r="V16" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>291</v>
+      </c>
+      <c r="B17" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" t="s">
+        <v>292</v>
+      </c>
+      <c r="D17" t="s">
+        <v>293</v>
+      </c>
+      <c r="E17" t="s">
+        <v>294</v>
+      </c>
+      <c r="F17" t="s">
+        <v>186</v>
+      </c>
+      <c r="G17" t="s">
+        <v>295</v>
+      </c>
+      <c r="H17">
+        <v>6025554276</v>
+      </c>
+      <c r="I17" t="s">
+        <v>296</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="L17" t="s">
+        <v>298</v>
+      </c>
+      <c r="M17">
+        <v>85004</v>
+      </c>
+      <c r="N17" t="s">
+        <v>299</v>
+      </c>
+      <c r="O17" t="s">
+        <v>300</v>
+      </c>
+      <c r="P17" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>301</v>
+      </c>
+      <c r="R17">
+        <v>85004</v>
+      </c>
+      <c r="S17" t="s">
+        <v>299</v>
+      </c>
+      <c r="T17" t="s">
+        <v>300</v>
+      </c>
+      <c r="U17" t="s">
+        <v>57</v>
+      </c>
+      <c r="V17" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>303</v>
+      </c>
+      <c r="B18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" t="s">
+        <v>304</v>
+      </c>
+      <c r="D18" t="s">
+        <v>305</v>
+      </c>
+      <c r="E18" t="s">
+        <v>306</v>
+      </c>
+      <c r="F18" t="s">
+        <v>307</v>
+      </c>
+      <c r="G18" t="s">
+        <v>308</v>
+      </c>
+      <c r="H18">
+        <v>2135557524</v>
+      </c>
+      <c r="I18" t="s">
+        <v>309</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="L18" t="s">
+        <v>311</v>
+      </c>
+      <c r="M18">
+        <v>90014</v>
+      </c>
+      <c r="N18" t="s">
+        <v>312</v>
+      </c>
+      <c r="O18" t="s">
+        <v>109</v>
+      </c>
+      <c r="P18" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>313</v>
+      </c>
+      <c r="R18">
+        <v>90017</v>
+      </c>
+      <c r="S18" t="s">
+        <v>312</v>
+      </c>
+      <c r="T18" t="s">
+        <v>109</v>
+      </c>
+      <c r="U18" t="s">
+        <v>57</v>
+      </c>
+      <c r="V18" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>315</v>
+      </c>
+      <c r="B19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" t="s">
+        <v>316</v>
+      </c>
+      <c r="D19" t="s">
+        <v>317</v>
+      </c>
+      <c r="E19" t="s">
+        <v>189</v>
+      </c>
+      <c r="F19" t="s">
+        <v>186</v>
+      </c>
+      <c r="G19" t="s">
+        <v>318</v>
+      </c>
+      <c r="H19">
+        <v>6125553948</v>
+      </c>
+      <c r="I19" t="s">
+        <v>319</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="L19" t="s">
+        <v>321</v>
+      </c>
+      <c r="M19">
+        <v>55402</v>
+      </c>
+      <c r="N19" t="s">
+        <v>322</v>
+      </c>
+      <c r="O19" t="s">
+        <v>323</v>
+      </c>
+      <c r="P19" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>324</v>
+      </c>
+      <c r="R19">
+        <v>55403</v>
+      </c>
+      <c r="S19" t="s">
+        <v>322</v>
+      </c>
+      <c r="T19" t="s">
+        <v>323</v>
+      </c>
+      <c r="U19" t="s">
+        <v>57</v>
+      </c>
+      <c r="V19" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>326</v>
+      </c>
+      <c r="B20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" t="s">
+        <v>327</v>
+      </c>
+      <c r="D20" t="s">
+        <v>328</v>
+      </c>
+      <c r="E20" t="s">
+        <v>329</v>
+      </c>
+      <c r="F20" t="s">
+        <v>194</v>
+      </c>
+      <c r="G20" t="s">
+        <v>330</v>
+      </c>
+      <c r="H20">
+        <v>6175558426</v>
+      </c>
+      <c r="I20" t="s">
+        <v>331</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="L20" t="s">
+        <v>333</v>
+      </c>
+      <c r="M20">
+        <v>2110</v>
+      </c>
+      <c r="N20" t="s">
+        <v>155</v>
+      </c>
+      <c r="O20" t="s">
+        <v>156</v>
+      </c>
+      <c r="P20" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>334</v>
+      </c>
+      <c r="R20">
+        <v>2110</v>
+      </c>
+      <c r="S20" t="s">
+        <v>155</v>
+      </c>
+      <c r="T20" t="s">
+        <v>156</v>
+      </c>
+      <c r="U20" t="s">
+        <v>57</v>
+      </c>
+      <c r="V20" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>336</v>
+      </c>
+      <c r="B21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" t="s">
+        <v>337</v>
+      </c>
+      <c r="D21" t="s">
+        <v>338</v>
+      </c>
+      <c r="E21" t="s">
+        <v>339</v>
+      </c>
+      <c r="F21" t="s">
+        <v>188</v>
+      </c>
+      <c r="G21" t="s">
+        <v>340</v>
+      </c>
+      <c r="H21">
+        <v>4155556198</v>
+      </c>
+      <c r="I21" t="s">
+        <v>341</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="L21" t="s">
+        <v>343</v>
+      </c>
+      <c r="M21">
+        <v>94108</v>
+      </c>
+      <c r="N21" t="s">
+        <v>108</v>
+      </c>
+      <c r="O21" t="s">
+        <v>109</v>
+      </c>
+      <c r="P21" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>344</v>
+      </c>
+      <c r="R21">
+        <v>94102</v>
+      </c>
+      <c r="S21" t="s">
+        <v>108</v>
+      </c>
+      <c r="T21" t="s">
+        <v>109</v>
+      </c>
+      <c r="U21" t="s">
+        <v>57</v>
+      </c>
+      <c r="V21" t="s">
+        <v>345</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="J6" r:id="rId1" display="https://example.com/" xr:uid="{07410863-7E42-984B-AF98-492906EACB5D}"/>
+    <hyperlink ref="K6" r:id="rId2" display="mailto:michael.anderson@example.com" xr:uid="{1EFE1173-A11D-744B-A188-9CB0E491578E}"/>
+    <hyperlink ref="J7" r:id="rId3" display="https://example.com/" xr:uid="{6CCF1265-C5FB-AE4C-B304-9C14CB317146}"/>
+    <hyperlink ref="K7" r:id="rId4" display="mailto:emma.wilson@example.com" xr:uid="{5C3020BB-5897-0A45-9E62-5F4795343F1F}"/>
+    <hyperlink ref="J8" r:id="rId5" display="https://example.com/" xr:uid="{1CF387DD-DE58-0D44-8542-9455231E2D29}"/>
+    <hyperlink ref="K8" r:id="rId6" display="mailto:william.harris@example.com" xr:uid="{3F77AADF-7EF2-B245-A0D2-32EE3D691A7D}"/>
+    <hyperlink ref="J9" r:id="rId7" display="https://example.com/" xr:uid="{D77A914B-0BE3-5A47-B602-809BEA21613B}"/>
+    <hyperlink ref="K9" r:id="rId8" display="mailto:ava.thompson@example.com" xr:uid="{44582F19-1503-2945-BBFA-44C42ABDAF73}"/>
+    <hyperlink ref="J10" r:id="rId9" display="https://example.com/" xr:uid="{56E4501F-A8FC-514C-9FFE-E272EDC40B4A}"/>
+    <hyperlink ref="K10" r:id="rId10" display="mailto:ethan.robinson@example.com" xr:uid="{69B49B1F-5100-DA46-8435-C6A4F9ED07E7}"/>
+    <hyperlink ref="J11" r:id="rId11" display="https://example.com/" xr:uid="{E9D9EA13-9188-484B-BD04-8B41169B0938}"/>
+    <hyperlink ref="K11" r:id="rId12" display="mailto:charlotte.davis@example.com" xr:uid="{9F72E2A2-A3DF-8C4E-AB79-19409B53A05C}"/>
+    <hyperlink ref="J12" r:id="rId13" display="https://example.com/" xr:uid="{12120336-22B2-ED4A-A1D8-1DA9FC221B52}"/>
+    <hyperlink ref="K12" r:id="rId14" display="mailto:james.parker@example.com" xr:uid="{A621E1CB-8D80-B54D-96ED-70323D4FB7C4}"/>
+    <hyperlink ref="J13" r:id="rId15" display="https://example.com/" xr:uid="{2D2FD434-A2DC-8E41-8342-B65229E269E7}"/>
+    <hyperlink ref="K13" r:id="rId16" display="mailto:isabella.moore@example.com" xr:uid="{8F64D154-5986-794B-B693-332B25E5DDF2}"/>
+    <hyperlink ref="J14" r:id="rId17" display="https://example.com/" xr:uid="{A9F37FA6-9689-A643-BAD1-B4BB570FEC6F}"/>
+    <hyperlink ref="K14" r:id="rId18" display="mailto:alexander.taylor@example.com" xr:uid="{FEE78697-E1D5-9444-AC67-D9D8E91D25AE}"/>
+    <hyperlink ref="J15" r:id="rId19" display="https://example.com/" xr:uid="{6102906B-FFCE-A642-9F93-E97CD89E7546}"/>
+    <hyperlink ref="K15" r:id="rId20" display="mailto:amelia.johnson@example.com" xr:uid="{52B9E300-7A6E-6B4C-B219-8BE3B08B19C6}"/>
+    <hyperlink ref="J16" r:id="rId21" display="https://example.com/" xr:uid="{787FD5A5-5291-1140-AAE2-3680350D265D}"/>
+    <hyperlink ref="K16" r:id="rId22" display="mailto:benjamin.clark@example.com" xr:uid="{BCE6DF2E-4816-DE4B-8DEF-5BCAD85A76EE}"/>
+    <hyperlink ref="J17" r:id="rId23" display="https://example.com/" xr:uid="{53D99FEC-B150-5C4E-977C-FB09EACA3FA1}"/>
+    <hyperlink ref="K17" r:id="rId24" display="mailto:mia.lewis@example.com" xr:uid="{3C60EBAF-8AD0-394A-BC01-0B2737F8C543}"/>
+    <hyperlink ref="J18" r:id="rId25" display="https://example.com/" xr:uid="{401A2EB3-EE13-A04A-A457-530FFE52F121}"/>
+    <hyperlink ref="K18" r:id="rId26" display="mailto:noah.walker@example.com" xr:uid="{30DDF0D9-A0B0-1145-8794-2F4F358A3363}"/>
+    <hyperlink ref="J19" r:id="rId27" display="https://example.com/" xr:uid="{CB247D6A-608B-8149-9898-6265C1620D2E}"/>
+    <hyperlink ref="K19" r:id="rId28" display="mailto:harper.hall@example.com" xr:uid="{4EDE485A-41EE-324B-9532-EC4D10D495E3}"/>
+    <hyperlink ref="J20" r:id="rId29" display="https://example.com/" xr:uid="{B0F88841-93B8-6846-BD69-11BC8136B513}"/>
+    <hyperlink ref="K20" r:id="rId30" display="mailto:lucas.young@example.com" xr:uid="{5DC79BCC-5F01-AC4C-9DE1-126DD5396065}"/>
+    <hyperlink ref="J21" r:id="rId31" display="https://example.com/" xr:uid="{DC4553B5-E71D-AF4F-B0E9-DB1886F21E1D}"/>
+    <hyperlink ref="K21" r:id="rId32" display="mailto:evelyn.king@example.com" xr:uid="{688CCA6B-8A7B-704E-BE6F-9156054CF9A9}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DE554E8-0B26-2E4E-8E00-4305FDECA419}">
+  <dimension ref="A1:SF13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:500" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="K1" s="10" t="s">
         <v>87</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
+      <c r="AA1" s="9"/>
+      <c r="AB1" s="9"/>
+      <c r="AC1" s="9"/>
+      <c r="AD1" s="9"/>
+      <c r="AE1" s="9"/>
+      <c r="AF1" s="9"/>
+      <c r="AG1" s="9"/>
+      <c r="AH1" s="9"/>
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="9"/>
+      <c r="AK1" s="9"/>
+      <c r="AL1" s="9"/>
+      <c r="AM1" s="9"/>
+      <c r="AN1" s="9"/>
+      <c r="AO1" s="9"/>
+      <c r="AP1" s="9"/>
+      <c r="AQ1" s="9"/>
+      <c r="AR1" s="9"/>
+      <c r="AS1" s="9"/>
+      <c r="AT1" s="9"/>
+      <c r="AU1" s="9"/>
+      <c r="AV1" s="9"/>
+      <c r="AW1" s="9"/>
+      <c r="AX1" s="9"/>
+      <c r="AY1" s="9"/>
+      <c r="AZ1" s="9"/>
+      <c r="BA1" s="9"/>
+      <c r="BB1" s="9"/>
+      <c r="BC1" s="9"/>
+      <c r="BD1" s="9"/>
+      <c r="BE1" s="9"/>
+      <c r="BF1" s="9"/>
+      <c r="BG1" s="9"/>
+      <c r="BH1" s="9"/>
+      <c r="BI1" s="9"/>
+      <c r="BJ1" s="9"/>
+      <c r="BK1" s="9"/>
+      <c r="BL1" s="9"/>
+      <c r="BM1" s="9"/>
+      <c r="BN1" s="9"/>
+      <c r="BO1" s="9"/>
+      <c r="BP1" s="9"/>
+      <c r="BQ1" s="9"/>
+      <c r="BR1" s="9"/>
+      <c r="BS1" s="9"/>
+      <c r="BT1" s="9"/>
+      <c r="BU1" s="9"/>
+      <c r="BV1" s="9"/>
+      <c r="BW1" s="9"/>
+      <c r="BX1" s="9"/>
+      <c r="BY1" s="9"/>
+      <c r="BZ1" s="9"/>
+      <c r="CA1" s="9"/>
+      <c r="CB1" s="9"/>
+      <c r="CC1" s="9"/>
+      <c r="CD1" s="9"/>
+      <c r="CE1" s="9"/>
+      <c r="CF1" s="9"/>
+      <c r="CG1" s="9"/>
+      <c r="CH1" s="9"/>
+      <c r="CI1" s="9"/>
+      <c r="CJ1" s="9"/>
+      <c r="CK1" s="9"/>
+      <c r="CL1" s="9"/>
+      <c r="CM1" s="9"/>
+      <c r="CN1" s="9"/>
+      <c r="CO1" s="9"/>
+      <c r="CP1" s="9"/>
+      <c r="CQ1" s="9"/>
+      <c r="CR1" s="9"/>
+      <c r="CS1" s="9"/>
+      <c r="CT1" s="9"/>
+      <c r="CU1" s="9"/>
+      <c r="CV1" s="9"/>
+      <c r="CW1" s="9"/>
+      <c r="CX1" s="9"/>
+      <c r="CY1" s="9"/>
+      <c r="CZ1" s="9"/>
+      <c r="DA1" s="9"/>
+      <c r="DB1" s="9"/>
+      <c r="DC1" s="9"/>
+      <c r="DD1" s="9"/>
+      <c r="DE1" s="9"/>
+      <c r="DF1" s="9"/>
+      <c r="DG1" s="9"/>
+      <c r="DH1" s="9"/>
+      <c r="DI1" s="9"/>
+      <c r="DJ1" s="9"/>
+      <c r="DK1" s="9"/>
+      <c r="DL1" s="9"/>
+      <c r="DM1" s="9"/>
+      <c r="DN1" s="9"/>
+      <c r="DO1" s="9"/>
+      <c r="DP1" s="9"/>
+      <c r="DQ1" s="9"/>
+      <c r="DR1" s="9"/>
+      <c r="DS1" s="9"/>
+      <c r="DT1" s="9"/>
+      <c r="DU1" s="9"/>
+      <c r="DV1" s="9"/>
+      <c r="DW1" s="9"/>
+      <c r="DX1" s="9"/>
+      <c r="DY1" s="9"/>
+      <c r="DZ1" s="9"/>
+      <c r="EA1" s="9"/>
+      <c r="EB1" s="9"/>
+      <c r="EC1" s="9"/>
+      <c r="ED1" s="9"/>
+      <c r="EE1" s="9"/>
+      <c r="EF1" s="9"/>
+      <c r="EG1" s="9"/>
+      <c r="EH1" s="9"/>
+      <c r="EI1" s="9"/>
+      <c r="EJ1" s="9"/>
+      <c r="EK1" s="9"/>
+      <c r="EL1" s="9"/>
+      <c r="EM1" s="9"/>
+      <c r="EN1" s="9"/>
+      <c r="EO1" s="9"/>
+      <c r="EP1" s="9"/>
+      <c r="EQ1" s="9"/>
+      <c r="ER1" s="9"/>
+      <c r="ES1" s="9"/>
+      <c r="ET1" s="9"/>
+      <c r="EU1" s="9"/>
+      <c r="EV1" s="9"/>
+      <c r="EW1" s="9"/>
+      <c r="EX1" s="9"/>
+      <c r="EY1" s="9"/>
+      <c r="EZ1" s="9"/>
+      <c r="FA1" s="9"/>
+      <c r="FB1" s="9"/>
+      <c r="FC1" s="9"/>
+      <c r="FD1" s="9"/>
+      <c r="FE1" s="9"/>
+      <c r="FF1" s="9"/>
+      <c r="FG1" s="9"/>
+      <c r="FH1" s="9"/>
+      <c r="FI1" s="9"/>
+      <c r="FJ1" s="9"/>
+      <c r="FK1" s="9"/>
+      <c r="FL1" s="9"/>
+      <c r="FM1" s="9"/>
+      <c r="FN1" s="9"/>
+      <c r="FO1" s="9"/>
+      <c r="FP1" s="9"/>
+      <c r="FQ1" s="9"/>
+      <c r="FR1" s="9"/>
+      <c r="FS1" s="9"/>
+      <c r="FT1" s="9"/>
+      <c r="FU1" s="9"/>
+      <c r="FV1" s="9"/>
+      <c r="FW1" s="9"/>
+      <c r="FX1" s="9"/>
+      <c r="FY1" s="9"/>
+      <c r="FZ1" s="9"/>
+      <c r="GA1" s="9"/>
+      <c r="GB1" s="9"/>
+      <c r="GC1" s="9"/>
+      <c r="GD1" s="9"/>
+      <c r="GE1" s="9"/>
+      <c r="GF1" s="9"/>
+      <c r="GG1" s="9"/>
+      <c r="GH1" s="9"/>
+      <c r="GI1" s="9"/>
+      <c r="GJ1" s="9"/>
+      <c r="GK1" s="9"/>
+      <c r="GL1" s="9"/>
+      <c r="GM1" s="9"/>
+      <c r="GN1" s="9"/>
+      <c r="GO1" s="9"/>
+      <c r="GP1" s="9"/>
+      <c r="GQ1" s="9"/>
+      <c r="GR1" s="9"/>
+      <c r="GS1" s="9"/>
+      <c r="GT1" s="9"/>
+      <c r="GU1" s="9"/>
+      <c r="GV1" s="9"/>
+      <c r="GW1" s="9"/>
+      <c r="GX1" s="9"/>
+      <c r="GY1" s="9"/>
+      <c r="GZ1" s="9"/>
+      <c r="HA1" s="9"/>
+      <c r="HB1" s="9"/>
+      <c r="HC1" s="9"/>
+      <c r="HD1" s="9"/>
+      <c r="HE1" s="9"/>
+      <c r="HF1" s="9"/>
+      <c r="HG1" s="9"/>
+      <c r="HH1" s="9"/>
+      <c r="HI1" s="9"/>
+      <c r="HJ1" s="9"/>
+      <c r="HK1" s="9"/>
+      <c r="HL1" s="9"/>
+      <c r="HM1" s="9"/>
+      <c r="HN1" s="9"/>
+      <c r="HO1" s="9"/>
+      <c r="HP1" s="9"/>
+      <c r="HQ1" s="9"/>
+      <c r="HR1" s="9"/>
+      <c r="HS1" s="9"/>
+      <c r="HT1" s="9"/>
+      <c r="HU1" s="9"/>
+      <c r="HV1" s="9"/>
+      <c r="HW1" s="9"/>
+      <c r="HX1" s="9"/>
+      <c r="HY1" s="9"/>
+      <c r="HZ1" s="9"/>
+      <c r="IA1" s="9"/>
+      <c r="IB1" s="9"/>
+      <c r="IC1" s="9"/>
+      <c r="ID1" s="9"/>
+      <c r="IE1" s="9"/>
+      <c r="IF1" s="9"/>
+      <c r="IG1" s="9"/>
+      <c r="IH1" s="9"/>
+      <c r="II1" s="9"/>
+      <c r="IJ1" s="9"/>
+      <c r="IK1" s="9"/>
+      <c r="IL1" s="9"/>
+      <c r="IM1" s="9"/>
+      <c r="IN1" s="9"/>
+      <c r="IO1" s="9"/>
+      <c r="IP1" s="9"/>
+      <c r="IQ1" s="9"/>
+      <c r="IR1" s="9"/>
+      <c r="IS1" s="9"/>
+      <c r="IT1" s="9"/>
+      <c r="IU1" s="9"/>
+      <c r="IV1" s="9"/>
+      <c r="IW1" s="9"/>
+      <c r="IX1" s="9"/>
+      <c r="IY1" s="9"/>
+      <c r="IZ1" s="9"/>
+      <c r="JA1" s="9"/>
+      <c r="JB1" s="9"/>
+      <c r="JC1" s="9"/>
+      <c r="JD1" s="9"/>
+      <c r="JE1" s="9"/>
+      <c r="JF1" s="9"/>
+      <c r="JG1" s="9"/>
+      <c r="JH1" s="9"/>
+      <c r="JI1" s="9"/>
+      <c r="JJ1" s="9"/>
+      <c r="JK1" s="9"/>
+      <c r="JL1" s="9"/>
+      <c r="JM1" s="9"/>
+      <c r="JN1" s="9"/>
+      <c r="JO1" s="9"/>
+      <c r="JP1" s="9"/>
+      <c r="JQ1" s="9"/>
+      <c r="JR1" s="9"/>
+      <c r="JS1" s="9"/>
+      <c r="JT1" s="9"/>
+      <c r="JU1" s="9"/>
+      <c r="JV1" s="9"/>
+      <c r="JW1" s="9"/>
+      <c r="JX1" s="9"/>
+      <c r="JY1" s="9"/>
+      <c r="JZ1" s="9"/>
+      <c r="KA1" s="9"/>
+      <c r="KB1" s="9"/>
+      <c r="KC1" s="9"/>
+      <c r="KD1" s="9"/>
+      <c r="KE1" s="9"/>
+      <c r="KF1" s="9"/>
+      <c r="KG1" s="9"/>
+      <c r="KH1" s="9"/>
+      <c r="KI1" s="9"/>
+      <c r="KJ1" s="9"/>
+      <c r="KK1" s="9"/>
+      <c r="KL1" s="9"/>
+      <c r="KM1" s="9"/>
+      <c r="KN1" s="9"/>
+      <c r="KO1" s="9"/>
+      <c r="KP1" s="9"/>
+      <c r="KQ1" s="9"/>
+      <c r="KR1" s="9"/>
+      <c r="KS1" s="9"/>
+      <c r="KT1" s="9"/>
+      <c r="KU1" s="9"/>
+      <c r="KV1" s="9"/>
+      <c r="KW1" s="9"/>
+      <c r="KX1" s="9"/>
+      <c r="KY1" s="9"/>
+      <c r="KZ1" s="9"/>
+      <c r="LA1" s="9"/>
+      <c r="LB1" s="9"/>
+      <c r="LC1" s="9"/>
+      <c r="LD1" s="9"/>
+      <c r="LE1" s="9"/>
+      <c r="LF1" s="9"/>
+      <c r="LG1" s="9"/>
+      <c r="LH1" s="9"/>
+      <c r="LI1" s="9"/>
+      <c r="LJ1" s="9"/>
+      <c r="LK1" s="9"/>
+      <c r="LL1" s="9"/>
+      <c r="LM1" s="9"/>
+      <c r="LN1" s="9"/>
+      <c r="LO1" s="9"/>
+      <c r="LP1" s="9"/>
+      <c r="LQ1" s="9"/>
+      <c r="LR1" s="9"/>
+      <c r="LS1" s="9"/>
+      <c r="LT1" s="9"/>
+      <c r="LU1" s="9"/>
+      <c r="LV1" s="9"/>
+      <c r="LW1" s="9"/>
+      <c r="LX1" s="9"/>
+      <c r="LY1" s="9"/>
+      <c r="LZ1" s="9"/>
+      <c r="MA1" s="9"/>
+      <c r="MB1" s="9"/>
+      <c r="MC1" s="9"/>
+      <c r="MD1" s="9"/>
+      <c r="ME1" s="9"/>
+      <c r="MF1" s="9"/>
+      <c r="MG1" s="9"/>
+      <c r="MH1" s="9"/>
+      <c r="MI1" s="9"/>
+      <c r="MJ1" s="9"/>
+      <c r="MK1" s="9"/>
+      <c r="ML1" s="9"/>
+      <c r="MM1" s="9"/>
+      <c r="MN1" s="9"/>
+      <c r="MO1" s="9"/>
+      <c r="MP1" s="9"/>
+      <c r="MQ1" s="9"/>
+      <c r="MR1" s="9"/>
+      <c r="MS1" s="9"/>
+      <c r="MT1" s="9"/>
+      <c r="MU1" s="9"/>
+      <c r="MV1" s="9"/>
+      <c r="MW1" s="9"/>
+      <c r="MX1" s="9"/>
+      <c r="MY1" s="9"/>
+      <c r="MZ1" s="9"/>
+      <c r="NA1" s="9"/>
+      <c r="NB1" s="9"/>
+      <c r="NC1" s="9"/>
+      <c r="ND1" s="9"/>
+      <c r="NE1" s="9"/>
+      <c r="NF1" s="9"/>
+      <c r="NG1" s="9"/>
+      <c r="NH1" s="9"/>
+      <c r="NI1" s="9"/>
+      <c r="NJ1" s="9"/>
+      <c r="NK1" s="9"/>
+      <c r="NL1" s="9"/>
+      <c r="NM1" s="9"/>
+      <c r="NN1" s="9"/>
+      <c r="NO1" s="9"/>
+      <c r="NP1" s="9"/>
+      <c r="NQ1" s="9"/>
+      <c r="NR1" s="9"/>
+      <c r="NS1" s="9"/>
+      <c r="NT1" s="9"/>
+      <c r="NU1" s="9"/>
+      <c r="NV1" s="9"/>
+      <c r="NW1" s="9"/>
+      <c r="NX1" s="9"/>
+      <c r="NY1" s="9"/>
+      <c r="NZ1" s="9"/>
+      <c r="OA1" s="9"/>
+      <c r="OB1" s="9"/>
+      <c r="OC1" s="9"/>
+      <c r="OD1" s="9"/>
+      <c r="OE1" s="9"/>
+      <c r="OF1" s="9"/>
+      <c r="OG1" s="9"/>
+      <c r="OH1" s="9"/>
+      <c r="OI1" s="9"/>
+      <c r="OJ1" s="9"/>
+      <c r="OK1" s="9"/>
+      <c r="OL1" s="9"/>
+      <c r="OM1" s="9"/>
+      <c r="ON1" s="9"/>
+      <c r="OO1" s="9"/>
+      <c r="OP1" s="9"/>
+      <c r="OQ1" s="9"/>
+      <c r="OR1" s="9"/>
+      <c r="OS1" s="9"/>
+      <c r="OT1" s="9"/>
+      <c r="OU1" s="9"/>
+      <c r="OV1" s="9"/>
+      <c r="OW1" s="9"/>
+      <c r="OX1" s="9"/>
+      <c r="OY1" s="9"/>
+      <c r="OZ1" s="9"/>
+      <c r="PA1" s="9"/>
+      <c r="PB1" s="9"/>
+      <c r="PC1" s="9"/>
+      <c r="PD1" s="9"/>
+      <c r="PE1" s="9"/>
+      <c r="PF1" s="9"/>
+      <c r="PG1" s="9"/>
+      <c r="PH1" s="9"/>
+      <c r="PI1" s="9"/>
+      <c r="PJ1" s="9"/>
+      <c r="PK1" s="9"/>
+      <c r="PL1" s="9"/>
+      <c r="PM1" s="9"/>
+      <c r="PN1" s="9"/>
+      <c r="PO1" s="9"/>
+      <c r="PP1" s="9"/>
+      <c r="PQ1" s="9"/>
+      <c r="PR1" s="9"/>
+      <c r="PS1" s="9"/>
+      <c r="PT1" s="9"/>
+      <c r="PU1" s="9"/>
+      <c r="PV1" s="9"/>
+      <c r="PW1" s="9"/>
+      <c r="PX1" s="9"/>
+      <c r="PY1" s="9"/>
+      <c r="PZ1" s="9"/>
+      <c r="QA1" s="9"/>
+      <c r="QB1" s="9"/>
+      <c r="QC1" s="9"/>
+      <c r="QD1" s="9"/>
+      <c r="QE1" s="9"/>
+      <c r="QF1" s="9"/>
+      <c r="QG1" s="9"/>
+      <c r="QH1" s="9"/>
+      <c r="QI1" s="9"/>
+      <c r="QJ1" s="9"/>
+      <c r="QK1" s="9"/>
+      <c r="QL1" s="9"/>
+      <c r="QM1" s="9"/>
+      <c r="QN1" s="9"/>
+      <c r="QO1" s="9"/>
+      <c r="QP1" s="9"/>
+      <c r="QQ1" s="9"/>
+      <c r="QR1" s="9"/>
+      <c r="QS1" s="9"/>
+      <c r="QT1" s="9"/>
+      <c r="QU1" s="9"/>
+      <c r="QV1" s="9"/>
+      <c r="QW1" s="9"/>
+      <c r="QX1" s="9"/>
+      <c r="QY1" s="9"/>
+      <c r="QZ1" s="9"/>
+      <c r="RA1" s="9"/>
+      <c r="RB1" s="9"/>
+      <c r="RC1" s="9"/>
+      <c r="RD1" s="9"/>
+      <c r="RE1" s="9"/>
+      <c r="RF1" s="9"/>
+      <c r="RG1" s="9"/>
+      <c r="RH1" s="9"/>
+      <c r="RI1" s="9"/>
+      <c r="RJ1" s="9"/>
+      <c r="RK1" s="9"/>
+      <c r="RL1" s="9"/>
+      <c r="RM1" s="9"/>
+      <c r="RN1" s="9"/>
+      <c r="RO1" s="9"/>
+      <c r="RP1" s="9"/>
+      <c r="RQ1" s="9"/>
+      <c r="RR1" s="9"/>
+      <c r="RS1" s="9"/>
+      <c r="RT1" s="9"/>
+      <c r="RU1" s="9"/>
+      <c r="RV1" s="9"/>
+      <c r="RW1" s="9"/>
+      <c r="RX1" s="9"/>
+      <c r="RY1" s="9"/>
+      <c r="RZ1" s="9"/>
+      <c r="SA1" s="9"/>
+      <c r="SB1" s="9"/>
+      <c r="SC1" s="9"/>
+      <c r="SD1" s="9"/>
+      <c r="SE1" s="9"/>
+      <c r="SF1" s="9"/>
+    </row>
+    <row r="2" spans="1:500" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2">
+        <v>2125550147</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="F2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2">
+        <v>10001</v>
+      </c>
+      <c r="H2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I2" t="s">
+        <v>102</v>
+      </c>
+      <c r="J2" t="s">
+        <v>103</v>
+      </c>
+      <c r="K2" t="s">
+        <v>96</v>
+      </c>
+      <c r="L2">
+        <v>10002</v>
+      </c>
+      <c r="M2" t="s">
+        <v>102</v>
+      </c>
+      <c r="N2" t="s">
+        <v>102</v>
+      </c>
+      <c r="O2" t="s">
+        <v>103</v>
+      </c>
+      <c r="P2" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
+      <c r="AC2" s="9"/>
+      <c r="AD2" s="9"/>
+      <c r="AE2" s="9"/>
+      <c r="AF2" s="9"/>
+      <c r="AG2" s="9"/>
+      <c r="AH2" s="9"/>
+      <c r="AI2" s="9"/>
+      <c r="AJ2" s="9"/>
+      <c r="AK2" s="9"/>
+      <c r="AL2" s="9"/>
+      <c r="AM2" s="9"/>
+      <c r="AN2" s="9"/>
+      <c r="AO2" s="9"/>
+      <c r="AP2" s="9"/>
+      <c r="AQ2" s="9"/>
+      <c r="AR2" s="9"/>
+      <c r="AS2" s="9"/>
+      <c r="AT2" s="9"/>
+      <c r="AU2" s="9"/>
+      <c r="AV2" s="9"/>
+      <c r="AW2" s="9"/>
+      <c r="AX2" s="9"/>
+      <c r="AY2" s="9"/>
+      <c r="AZ2" s="9"/>
+      <c r="BA2" s="9"/>
+      <c r="BB2" s="9"/>
+      <c r="BC2" s="9"/>
+      <c r="BD2" s="9"/>
+      <c r="BE2" s="9"/>
+      <c r="BF2" s="9"/>
+      <c r="BG2" s="9"/>
+      <c r="BH2" s="9"/>
+      <c r="BI2" s="9"/>
+      <c r="BJ2" s="9"/>
+      <c r="BK2" s="9"/>
+      <c r="BL2" s="9"/>
+      <c r="BM2" s="9"/>
+      <c r="BN2" s="9"/>
+      <c r="BO2" s="9"/>
+      <c r="BP2" s="9"/>
+      <c r="BQ2" s="9"/>
+      <c r="BR2" s="9"/>
+      <c r="BS2" s="9"/>
+      <c r="BT2" s="9"/>
+      <c r="BU2" s="9"/>
+      <c r="BV2" s="9"/>
+      <c r="BW2" s="9"/>
+      <c r="BX2" s="9"/>
+      <c r="BY2" s="9"/>
+      <c r="BZ2" s="9"/>
+      <c r="CA2" s="9"/>
+      <c r="CB2" s="9"/>
+      <c r="CC2" s="9"/>
+      <c r="CD2" s="9"/>
+      <c r="CE2" s="9"/>
+      <c r="CF2" s="9"/>
+      <c r="CG2" s="9"/>
+      <c r="CH2" s="9"/>
+      <c r="CI2" s="9"/>
+      <c r="CJ2" s="9"/>
+      <c r="CK2" s="9"/>
+      <c r="CL2" s="9"/>
+      <c r="CM2" s="9"/>
+      <c r="CN2" s="9"/>
+      <c r="CO2" s="9"/>
+      <c r="CP2" s="9"/>
+      <c r="CQ2" s="9"/>
+      <c r="CR2" s="9"/>
+      <c r="CS2" s="9"/>
+      <c r="CT2" s="9"/>
+      <c r="CU2" s="9"/>
+      <c r="CV2" s="9"/>
+      <c r="CW2" s="9"/>
+      <c r="CX2" s="9"/>
+      <c r="CY2" s="9"/>
+      <c r="CZ2" s="9"/>
+      <c r="DA2" s="9"/>
+      <c r="DB2" s="9"/>
+      <c r="DC2" s="9"/>
+      <c r="DD2" s="9"/>
+      <c r="DE2" s="9"/>
+      <c r="DF2" s="9"/>
+      <c r="DG2" s="9"/>
+      <c r="DH2" s="9"/>
+      <c r="DI2" s="9"/>
+      <c r="DJ2" s="9"/>
+      <c r="DK2" s="9"/>
+      <c r="DL2" s="9"/>
+      <c r="DM2" s="9"/>
+      <c r="DN2" s="9"/>
+      <c r="DO2" s="9"/>
+      <c r="DP2" s="9"/>
+      <c r="DQ2" s="9"/>
+      <c r="DR2" s="9"/>
+      <c r="DS2" s="9"/>
+      <c r="DT2" s="9"/>
+      <c r="DU2" s="9"/>
+      <c r="DV2" s="9"/>
+      <c r="DW2" s="9"/>
+      <c r="DX2" s="9"/>
+      <c r="DY2" s="9"/>
+      <c r="DZ2" s="9"/>
+      <c r="EA2" s="9"/>
+      <c r="EB2" s="9"/>
+      <c r="EC2" s="9"/>
+      <c r="ED2" s="9"/>
+      <c r="EE2" s="9"/>
+      <c r="EF2" s="9"/>
+      <c r="EG2" s="9"/>
+      <c r="EH2" s="9"/>
+      <c r="EI2" s="9"/>
+      <c r="EJ2" s="9"/>
+      <c r="EK2" s="9"/>
+      <c r="EL2" s="9"/>
+      <c r="EM2" s="9"/>
+      <c r="EN2" s="9"/>
+      <c r="EO2" s="9"/>
+      <c r="EP2" s="9"/>
+      <c r="EQ2" s="9"/>
+      <c r="ER2" s="9"/>
+      <c r="ES2" s="9"/>
+      <c r="ET2" s="9"/>
+      <c r="EU2" s="9"/>
+      <c r="EV2" s="9"/>
+      <c r="EW2" s="9"/>
+      <c r="EX2" s="9"/>
+      <c r="EY2" s="9"/>
+      <c r="EZ2" s="9"/>
+      <c r="FA2" s="9"/>
+      <c r="FB2" s="9"/>
+      <c r="FC2" s="9"/>
+      <c r="FD2" s="9"/>
+      <c r="FE2" s="9"/>
+      <c r="FF2" s="9"/>
+      <c r="FG2" s="9"/>
+      <c r="FH2" s="9"/>
+      <c r="FI2" s="9"/>
+      <c r="FJ2" s="9"/>
+      <c r="FK2" s="9"/>
+      <c r="FL2" s="9"/>
+      <c r="FM2" s="9"/>
+      <c r="FN2" s="9"/>
+      <c r="FO2" s="9"/>
+      <c r="FP2" s="9"/>
+      <c r="FQ2" s="9"/>
+      <c r="FR2" s="9"/>
+      <c r="FS2" s="9"/>
+      <c r="FT2" s="9"/>
+      <c r="FU2" s="9"/>
+      <c r="FV2" s="9"/>
+      <c r="FW2" s="9"/>
+      <c r="FX2" s="9"/>
+      <c r="FY2" s="9"/>
+      <c r="FZ2" s="9"/>
+      <c r="GA2" s="9"/>
+      <c r="GB2" s="9"/>
+      <c r="GC2" s="9"/>
+      <c r="GD2" s="9"/>
+      <c r="GE2" s="9"/>
+      <c r="GF2" s="9"/>
+      <c r="GG2" s="9"/>
+      <c r="GH2" s="9"/>
+      <c r="GI2" s="9"/>
+      <c r="GJ2" s="9"/>
+      <c r="GK2" s="9"/>
+      <c r="GL2" s="9"/>
+      <c r="GM2" s="9"/>
+      <c r="GN2" s="9"/>
+      <c r="GO2" s="9"/>
+      <c r="GP2" s="9"/>
+      <c r="GQ2" s="9"/>
+      <c r="GR2" s="9"/>
+      <c r="GS2" s="9"/>
+      <c r="GT2" s="9"/>
+      <c r="GU2" s="9"/>
+      <c r="GV2" s="9"/>
+      <c r="GW2" s="9"/>
+      <c r="GX2" s="9"/>
+      <c r="GY2" s="9"/>
+      <c r="GZ2" s="9"/>
+      <c r="HA2" s="9"/>
+      <c r="HB2" s="9"/>
+      <c r="HC2" s="9"/>
+      <c r="HD2" s="9"/>
+      <c r="HE2" s="9"/>
+      <c r="HF2" s="9"/>
+      <c r="HG2" s="9"/>
+      <c r="HH2" s="9"/>
+      <c r="HI2" s="9"/>
+      <c r="HJ2" s="9"/>
+      <c r="HK2" s="9"/>
+      <c r="HL2" s="9"/>
+      <c r="HM2" s="9"/>
+      <c r="HN2" s="9"/>
+      <c r="HO2" s="9"/>
+      <c r="HP2" s="9"/>
+      <c r="HQ2" s="9"/>
+      <c r="HR2" s="9"/>
+      <c r="HS2" s="9"/>
+      <c r="HT2" s="9"/>
+      <c r="HU2" s="9"/>
+      <c r="HV2" s="9"/>
+      <c r="HW2" s="9"/>
+      <c r="HX2" s="9"/>
+      <c r="HY2" s="9"/>
+      <c r="HZ2" s="9"/>
+      <c r="IA2" s="9"/>
+      <c r="IB2" s="9"/>
+      <c r="IC2" s="9"/>
+      <c r="ID2" s="9"/>
+      <c r="IE2" s="9"/>
+      <c r="IF2" s="9"/>
+      <c r="IG2" s="9"/>
+      <c r="IH2" s="9"/>
+      <c r="II2" s="9"/>
+      <c r="IJ2" s="9"/>
+      <c r="IK2" s="9"/>
+      <c r="IL2" s="9"/>
+      <c r="IM2" s="9"/>
+      <c r="IN2" s="9"/>
+      <c r="IO2" s="9"/>
+      <c r="IP2" s="9"/>
+      <c r="IQ2" s="9"/>
+      <c r="IR2" s="9"/>
+      <c r="IS2" s="9"/>
+      <c r="IT2" s="9"/>
+      <c r="IU2" s="9"/>
+      <c r="IV2" s="9"/>
+      <c r="IW2" s="9"/>
+      <c r="IX2" s="9"/>
+      <c r="IY2" s="9"/>
+      <c r="IZ2" s="9"/>
+      <c r="JA2" s="9"/>
+      <c r="JB2" s="9"/>
+      <c r="JC2" s="9"/>
+      <c r="JD2" s="9"/>
+      <c r="JE2" s="9"/>
+      <c r="JF2" s="9"/>
+      <c r="JG2" s="9"/>
+      <c r="JH2" s="9"/>
+      <c r="JI2" s="9"/>
+      <c r="JJ2" s="9"/>
+      <c r="JK2" s="9"/>
+      <c r="JL2" s="9"/>
+      <c r="JM2" s="9"/>
+      <c r="JN2" s="9"/>
+      <c r="JO2" s="9"/>
+      <c r="JP2" s="9"/>
+      <c r="JQ2" s="9"/>
+      <c r="JR2" s="9"/>
+      <c r="JS2" s="9"/>
+      <c r="JT2" s="9"/>
+      <c r="JU2" s="9"/>
+      <c r="JV2" s="9"/>
+      <c r="JW2" s="9"/>
+      <c r="JX2" s="9"/>
+      <c r="JY2" s="9"/>
+      <c r="JZ2" s="9"/>
+      <c r="KA2" s="9"/>
+      <c r="KB2" s="9"/>
+      <c r="KC2" s="9"/>
+      <c r="KD2" s="9"/>
+      <c r="KE2" s="9"/>
+      <c r="KF2" s="9"/>
+      <c r="KG2" s="9"/>
+      <c r="KH2" s="9"/>
+      <c r="KI2" s="9"/>
+      <c r="KJ2" s="9"/>
+      <c r="KK2" s="9"/>
+      <c r="KL2" s="9"/>
+      <c r="KM2" s="9"/>
+      <c r="KN2" s="9"/>
+      <c r="KO2" s="9"/>
+      <c r="KP2" s="9"/>
+      <c r="KQ2" s="9"/>
+      <c r="KR2" s="9"/>
+      <c r="KS2" s="9"/>
+      <c r="KT2" s="9"/>
+      <c r="KU2" s="9"/>
+      <c r="KV2" s="9"/>
+      <c r="KW2" s="9"/>
+      <c r="KX2" s="9"/>
+      <c r="KY2" s="9"/>
+      <c r="KZ2" s="9"/>
+      <c r="LA2" s="9"/>
+      <c r="LB2" s="9"/>
+      <c r="LC2" s="9"/>
+      <c r="LD2" s="9"/>
+      <c r="LE2" s="9"/>
+      <c r="LF2" s="9"/>
+      <c r="LG2" s="9"/>
+      <c r="LH2" s="9"/>
+      <c r="LI2" s="9"/>
+      <c r="LJ2" s="9"/>
+      <c r="LK2" s="9"/>
+      <c r="LL2" s="9"/>
+      <c r="LM2" s="9"/>
+      <c r="LN2" s="9"/>
+      <c r="LO2" s="9"/>
+      <c r="LP2" s="9"/>
+      <c r="LQ2" s="9"/>
+      <c r="LR2" s="9"/>
+      <c r="LS2" s="9"/>
+      <c r="LT2" s="9"/>
+      <c r="LU2" s="9"/>
+      <c r="LV2" s="9"/>
+      <c r="LW2" s="9"/>
+      <c r="LX2" s="9"/>
+      <c r="LY2" s="9"/>
+      <c r="LZ2" s="9"/>
+      <c r="MA2" s="9"/>
+      <c r="MB2" s="9"/>
+      <c r="MC2" s="9"/>
+      <c r="MD2" s="9"/>
+      <c r="ME2" s="9"/>
+      <c r="MF2" s="9"/>
+      <c r="MG2" s="9"/>
+      <c r="MH2" s="9"/>
+      <c r="MI2" s="9"/>
+      <c r="MJ2" s="9"/>
+      <c r="MK2" s="9"/>
+      <c r="ML2" s="9"/>
+      <c r="MM2" s="9"/>
+      <c r="MN2" s="9"/>
+      <c r="MO2" s="9"/>
+      <c r="MP2" s="9"/>
+      <c r="MQ2" s="9"/>
+      <c r="MR2" s="9"/>
+      <c r="MS2" s="9"/>
+      <c r="MT2" s="9"/>
+      <c r="MU2" s="9"/>
+      <c r="MV2" s="9"/>
+      <c r="MW2" s="9"/>
+      <c r="MX2" s="9"/>
+      <c r="MY2" s="9"/>
+      <c r="MZ2" s="9"/>
+      <c r="NA2" s="9"/>
+      <c r="NB2" s="9"/>
+      <c r="NC2" s="9"/>
+      <c r="ND2" s="9"/>
+      <c r="NE2" s="9"/>
+      <c r="NF2" s="9"/>
+      <c r="NG2" s="9"/>
+      <c r="NH2" s="9"/>
+      <c r="NI2" s="9"/>
+      <c r="NJ2" s="9"/>
+      <c r="NK2" s="9"/>
+      <c r="NL2" s="9"/>
+      <c r="NM2" s="9"/>
+      <c r="NN2" s="9"/>
+      <c r="NO2" s="9"/>
+      <c r="NP2" s="9"/>
+      <c r="NQ2" s="9"/>
+      <c r="NR2" s="9"/>
+      <c r="NS2" s="9"/>
+      <c r="NT2" s="9"/>
+      <c r="NU2" s="9"/>
+      <c r="NV2" s="9"/>
+      <c r="NW2" s="9"/>
+      <c r="NX2" s="9"/>
+      <c r="NY2" s="9"/>
+      <c r="NZ2" s="9"/>
+      <c r="OA2" s="9"/>
+      <c r="OB2" s="9"/>
+      <c r="OC2" s="9"/>
+      <c r="OD2" s="9"/>
+      <c r="OE2" s="9"/>
+      <c r="OF2" s="9"/>
+      <c r="OG2" s="9"/>
+      <c r="OH2" s="9"/>
+      <c r="OI2" s="9"/>
+      <c r="OJ2" s="9"/>
+      <c r="OK2" s="9"/>
+      <c r="OL2" s="9"/>
+      <c r="OM2" s="9"/>
+      <c r="ON2" s="9"/>
+      <c r="OO2" s="9"/>
+      <c r="OP2" s="9"/>
+      <c r="OQ2" s="9"/>
+      <c r="OR2" s="9"/>
+      <c r="OS2" s="9"/>
+      <c r="OT2" s="9"/>
+      <c r="OU2" s="9"/>
+      <c r="OV2" s="9"/>
+      <c r="OW2" s="9"/>
+      <c r="OX2" s="9"/>
+      <c r="OY2" s="9"/>
+      <c r="OZ2" s="9"/>
+      <c r="PA2" s="9"/>
+      <c r="PB2" s="9"/>
+      <c r="PC2" s="9"/>
+      <c r="PD2" s="9"/>
+      <c r="PE2" s="9"/>
+      <c r="PF2" s="9"/>
+      <c r="PG2" s="9"/>
+      <c r="PH2" s="9"/>
+      <c r="PI2" s="9"/>
+      <c r="PJ2" s="9"/>
+      <c r="PK2" s="9"/>
+      <c r="PL2" s="9"/>
+      <c r="PM2" s="9"/>
+      <c r="PN2" s="9"/>
+      <c r="PO2" s="9"/>
+      <c r="PP2" s="9"/>
+      <c r="PQ2" s="9"/>
+      <c r="PR2" s="9"/>
+      <c r="PS2" s="9"/>
+      <c r="PT2" s="9"/>
+      <c r="PU2" s="9"/>
+      <c r="PV2" s="9"/>
+      <c r="PW2" s="9"/>
+      <c r="PX2" s="9"/>
+      <c r="PY2" s="9"/>
+      <c r="PZ2" s="9"/>
+      <c r="QA2" s="9"/>
+      <c r="QB2" s="9"/>
+      <c r="QC2" s="9"/>
+      <c r="QD2" s="9"/>
+      <c r="QE2" s="9"/>
+      <c r="QF2" s="9"/>
+      <c r="QG2" s="9"/>
+      <c r="QH2" s="9"/>
+      <c r="QI2" s="9"/>
+      <c r="QJ2" s="9"/>
+      <c r="QK2" s="9"/>
+      <c r="QL2" s="9"/>
+      <c r="QM2" s="9"/>
+      <c r="QN2" s="9"/>
+      <c r="QO2" s="9"/>
+      <c r="QP2" s="9"/>
+      <c r="QQ2" s="9"/>
+      <c r="QR2" s="9"/>
+      <c r="QS2" s="9"/>
+      <c r="QT2" s="9"/>
+      <c r="QU2" s="9"/>
+      <c r="QV2" s="9"/>
+      <c r="QW2" s="9"/>
+      <c r="QX2" s="9"/>
+      <c r="QY2" s="9"/>
+      <c r="QZ2" s="9"/>
+      <c r="RA2" s="9"/>
+      <c r="RB2" s="9"/>
+      <c r="RC2" s="9"/>
+      <c r="RD2" s="9"/>
+      <c r="RE2" s="9"/>
+      <c r="RF2" s="9"/>
+      <c r="RG2" s="9"/>
+      <c r="RH2" s="9"/>
+      <c r="RI2" s="9"/>
+      <c r="RJ2" s="9"/>
+      <c r="RK2" s="9"/>
+      <c r="RL2" s="9"/>
+      <c r="RM2" s="9"/>
+      <c r="RN2" s="9"/>
+      <c r="RO2" s="9"/>
+      <c r="RP2" s="9"/>
+      <c r="RQ2" s="9"/>
+      <c r="RR2" s="9"/>
+      <c r="RS2" s="9"/>
+      <c r="RT2" s="9"/>
+      <c r="RU2" s="9"/>
+      <c r="RV2" s="9"/>
+      <c r="RW2" s="9"/>
+      <c r="RX2" s="9"/>
+      <c r="RY2" s="9"/>
+      <c r="RZ2" s="9"/>
+      <c r="SA2" s="9"/>
+      <c r="SB2" s="9"/>
+      <c r="SC2" s="9"/>
+      <c r="SD2" s="9"/>
+      <c r="SE2" s="9"/>
+      <c r="SF2" s="9"/>
+    </row>
+    <row r="3" spans="1:500" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D3">
+        <v>3125550188</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="F3" t="s">
+        <v>104</v>
+      </c>
+      <c r="G3">
+        <v>60611</v>
+      </c>
+      <c r="H3" t="s">
+        <v>105</v>
+      </c>
+      <c r="I3" t="s">
+        <v>106</v>
+      </c>
+      <c r="J3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K3" t="s">
+        <v>107</v>
+      </c>
+      <c r="L3">
+        <v>60661</v>
+      </c>
+      <c r="M3" t="s">
+        <v>105</v>
+      </c>
+      <c r="N3" t="s">
+        <v>106</v>
+      </c>
+      <c r="O3" t="s">
+        <v>103</v>
+      </c>
+      <c r="P3" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="9"/>
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="9"/>
+      <c r="AB3" s="9"/>
+      <c r="AC3" s="9"/>
+      <c r="AD3" s="9"/>
+      <c r="AE3" s="9"/>
+      <c r="AF3" s="9"/>
+      <c r="AG3" s="9"/>
+      <c r="AH3" s="9"/>
+      <c r="AI3" s="9"/>
+      <c r="AJ3" s="9"/>
+      <c r="AK3" s="9"/>
+      <c r="AL3" s="9"/>
+      <c r="AM3" s="9"/>
+      <c r="AN3" s="9"/>
+      <c r="AO3" s="9"/>
+      <c r="AP3" s="9"/>
+      <c r="AQ3" s="9"/>
+      <c r="AR3" s="9"/>
+      <c r="AS3" s="9"/>
+      <c r="AT3" s="9"/>
+      <c r="AU3" s="9"/>
+      <c r="AV3" s="9"/>
+      <c r="AW3" s="9"/>
+      <c r="AX3" s="9"/>
+      <c r="AY3" s="9"/>
+      <c r="AZ3" s="9"/>
+      <c r="BA3" s="9"/>
+      <c r="BB3" s="9"/>
+      <c r="BC3" s="9"/>
+      <c r="BD3" s="9"/>
+      <c r="BE3" s="9"/>
+      <c r="BF3" s="9"/>
+      <c r="BG3" s="9"/>
+      <c r="BH3" s="9"/>
+      <c r="BI3" s="9"/>
+      <c r="BJ3" s="9"/>
+      <c r="BK3" s="9"/>
+      <c r="BL3" s="9"/>
+      <c r="BM3" s="9"/>
+      <c r="BN3" s="9"/>
+      <c r="BO3" s="9"/>
+      <c r="BP3" s="9"/>
+      <c r="BQ3" s="9"/>
+      <c r="BR3" s="9"/>
+      <c r="BS3" s="9"/>
+      <c r="BT3" s="9"/>
+      <c r="BU3" s="9"/>
+      <c r="BV3" s="9"/>
+      <c r="BW3" s="9"/>
+      <c r="BX3" s="9"/>
+      <c r="BY3" s="9"/>
+      <c r="BZ3" s="9"/>
+      <c r="CA3" s="9"/>
+      <c r="CB3" s="9"/>
+      <c r="CC3" s="9"/>
+      <c r="CD3" s="9"/>
+      <c r="CE3" s="9"/>
+      <c r="CF3" s="9"/>
+      <c r="CG3" s="9"/>
+      <c r="CH3" s="9"/>
+      <c r="CI3" s="9"/>
+      <c r="CJ3" s="9"/>
+      <c r="CK3" s="9"/>
+      <c r="CL3" s="9"/>
+      <c r="CM3" s="9"/>
+      <c r="CN3" s="9"/>
+      <c r="CO3" s="9"/>
+      <c r="CP3" s="9"/>
+      <c r="CQ3" s="9"/>
+      <c r="CR3" s="9"/>
+      <c r="CS3" s="9"/>
+      <c r="CT3" s="9"/>
+      <c r="CU3" s="9"/>
+      <c r="CV3" s="9"/>
+      <c r="CW3" s="9"/>
+      <c r="CX3" s="9"/>
+      <c r="CY3" s="9"/>
+      <c r="CZ3" s="9"/>
+      <c r="DA3" s="9"/>
+      <c r="DB3" s="9"/>
+      <c r="DC3" s="9"/>
+      <c r="DD3" s="9"/>
+      <c r="DE3" s="9"/>
+      <c r="DF3" s="9"/>
+      <c r="DG3" s="9"/>
+      <c r="DH3" s="9"/>
+      <c r="DI3" s="9"/>
+      <c r="DJ3" s="9"/>
+      <c r="DK3" s="9"/>
+      <c r="DL3" s="9"/>
+      <c r="DM3" s="9"/>
+      <c r="DN3" s="9"/>
+      <c r="DO3" s="9"/>
+      <c r="DP3" s="9"/>
+      <c r="DQ3" s="9"/>
+      <c r="DR3" s="9"/>
+      <c r="DS3" s="9"/>
+      <c r="DT3" s="9"/>
+      <c r="DU3" s="9"/>
+      <c r="DV3" s="9"/>
+      <c r="DW3" s="9"/>
+      <c r="DX3" s="9"/>
+      <c r="DY3" s="9"/>
+      <c r="DZ3" s="9"/>
+      <c r="EA3" s="9"/>
+      <c r="EB3" s="9"/>
+      <c r="EC3" s="9"/>
+      <c r="ED3" s="9"/>
+      <c r="EE3" s="9"/>
+      <c r="EF3" s="9"/>
+      <c r="EG3" s="9"/>
+      <c r="EH3" s="9"/>
+      <c r="EI3" s="9"/>
+      <c r="EJ3" s="9"/>
+      <c r="EK3" s="9"/>
+      <c r="EL3" s="9"/>
+      <c r="EM3" s="9"/>
+      <c r="EN3" s="9"/>
+      <c r="EO3" s="9"/>
+      <c r="EP3" s="9"/>
+      <c r="EQ3" s="9"/>
+      <c r="ER3" s="9"/>
+      <c r="ES3" s="9"/>
+      <c r="ET3" s="9"/>
+      <c r="EU3" s="9"/>
+      <c r="EV3" s="9"/>
+      <c r="EW3" s="9"/>
+      <c r="EX3" s="9"/>
+      <c r="EY3" s="9"/>
+      <c r="EZ3" s="9"/>
+      <c r="FA3" s="9"/>
+      <c r="FB3" s="9"/>
+      <c r="FC3" s="9"/>
+      <c r="FD3" s="9"/>
+      <c r="FE3" s="9"/>
+      <c r="FF3" s="9"/>
+      <c r="FG3" s="9"/>
+      <c r="FH3" s="9"/>
+      <c r="FI3" s="9"/>
+      <c r="FJ3" s="9"/>
+      <c r="FK3" s="9"/>
+      <c r="FL3" s="9"/>
+      <c r="FM3" s="9"/>
+      <c r="FN3" s="9"/>
+      <c r="FO3" s="9"/>
+      <c r="FP3" s="9"/>
+      <c r="FQ3" s="9"/>
+      <c r="FR3" s="9"/>
+      <c r="FS3" s="9"/>
+      <c r="FT3" s="9"/>
+      <c r="FU3" s="9"/>
+      <c r="FV3" s="9"/>
+      <c r="FW3" s="9"/>
+      <c r="FX3" s="9"/>
+      <c r="FY3" s="9"/>
+      <c r="FZ3" s="9"/>
+      <c r="GA3" s="9"/>
+      <c r="GB3" s="9"/>
+      <c r="GC3" s="9"/>
+      <c r="GD3" s="9"/>
+      <c r="GE3" s="9"/>
+      <c r="GF3" s="9"/>
+      <c r="GG3" s="9"/>
+      <c r="GH3" s="9"/>
+      <c r="GI3" s="9"/>
+      <c r="GJ3" s="9"/>
+      <c r="GK3" s="9"/>
+      <c r="GL3" s="9"/>
+      <c r="GM3" s="9"/>
+      <c r="GN3" s="9"/>
+      <c r="GO3" s="9"/>
+      <c r="GP3" s="9"/>
+      <c r="GQ3" s="9"/>
+      <c r="GR3" s="9"/>
+      <c r="GS3" s="9"/>
+      <c r="GT3" s="9"/>
+      <c r="GU3" s="9"/>
+      <c r="GV3" s="9"/>
+      <c r="GW3" s="9"/>
+      <c r="GX3" s="9"/>
+      <c r="GY3" s="9"/>
+      <c r="GZ3" s="9"/>
+      <c r="HA3" s="9"/>
+      <c r="HB3" s="9"/>
+      <c r="HC3" s="9"/>
+      <c r="HD3" s="9"/>
+      <c r="HE3" s="9"/>
+      <c r="HF3" s="9"/>
+      <c r="HG3" s="9"/>
+      <c r="HH3" s="9"/>
+      <c r="HI3" s="9"/>
+      <c r="HJ3" s="9"/>
+      <c r="HK3" s="9"/>
+      <c r="HL3" s="9"/>
+      <c r="HM3" s="9"/>
+      <c r="HN3" s="9"/>
+      <c r="HO3" s="9"/>
+      <c r="HP3" s="9"/>
+      <c r="HQ3" s="9"/>
+      <c r="HR3" s="9"/>
+      <c r="HS3" s="9"/>
+      <c r="HT3" s="9"/>
+      <c r="HU3" s="9"/>
+      <c r="HV3" s="9"/>
+      <c r="HW3" s="9"/>
+      <c r="HX3" s="9"/>
+      <c r="HY3" s="9"/>
+      <c r="HZ3" s="9"/>
+      <c r="IA3" s="9"/>
+      <c r="IB3" s="9"/>
+      <c r="IC3" s="9"/>
+      <c r="ID3" s="9"/>
+      <c r="IE3" s="9"/>
+      <c r="IF3" s="9"/>
+      <c r="IG3" s="9"/>
+      <c r="IH3" s="9"/>
+      <c r="II3" s="9"/>
+      <c r="IJ3" s="9"/>
+      <c r="IK3" s="9"/>
+      <c r="IL3" s="9"/>
+      <c r="IM3" s="9"/>
+      <c r="IN3" s="9"/>
+      <c r="IO3" s="9"/>
+      <c r="IP3" s="9"/>
+      <c r="IQ3" s="9"/>
+      <c r="IR3" s="9"/>
+      <c r="IS3" s="9"/>
+      <c r="IT3" s="9"/>
+      <c r="IU3" s="9"/>
+      <c r="IV3" s="9"/>
+      <c r="IW3" s="9"/>
+      <c r="IX3" s="9"/>
+      <c r="IY3" s="9"/>
+      <c r="IZ3" s="9"/>
+      <c r="JA3" s="9"/>
+      <c r="JB3" s="9"/>
+      <c r="JC3" s="9"/>
+      <c r="JD3" s="9"/>
+      <c r="JE3" s="9"/>
+      <c r="JF3" s="9"/>
+      <c r="JG3" s="9"/>
+      <c r="JH3" s="9"/>
+      <c r="JI3" s="9"/>
+      <c r="JJ3" s="9"/>
+      <c r="JK3" s="9"/>
+      <c r="JL3" s="9"/>
+      <c r="JM3" s="9"/>
+      <c r="JN3" s="9"/>
+      <c r="JO3" s="9"/>
+      <c r="JP3" s="9"/>
+      <c r="JQ3" s="9"/>
+      <c r="JR3" s="9"/>
+      <c r="JS3" s="9"/>
+      <c r="JT3" s="9"/>
+      <c r="JU3" s="9"/>
+      <c r="JV3" s="9"/>
+      <c r="JW3" s="9"/>
+      <c r="JX3" s="9"/>
+      <c r="JY3" s="9"/>
+      <c r="JZ3" s="9"/>
+      <c r="KA3" s="9"/>
+      <c r="KB3" s="9"/>
+      <c r="KC3" s="9"/>
+      <c r="KD3" s="9"/>
+      <c r="KE3" s="9"/>
+      <c r="KF3" s="9"/>
+      <c r="KG3" s="9"/>
+      <c r="KH3" s="9"/>
+      <c r="KI3" s="9"/>
+      <c r="KJ3" s="9"/>
+      <c r="KK3" s="9"/>
+      <c r="KL3" s="9"/>
+      <c r="KM3" s="9"/>
+      <c r="KN3" s="9"/>
+      <c r="KO3" s="9"/>
+      <c r="KP3" s="9"/>
+      <c r="KQ3" s="9"/>
+      <c r="KR3" s="9"/>
+      <c r="KS3" s="9"/>
+      <c r="KT3" s="9"/>
+      <c r="KU3" s="9"/>
+      <c r="KV3" s="9"/>
+      <c r="KW3" s="9"/>
+      <c r="KX3" s="9"/>
+      <c r="KY3" s="9"/>
+      <c r="KZ3" s="9"/>
+      <c r="LA3" s="9"/>
+      <c r="LB3" s="9"/>
+      <c r="LC3" s="9"/>
+      <c r="LD3" s="9"/>
+      <c r="LE3" s="9"/>
+      <c r="LF3" s="9"/>
+      <c r="LG3" s="9"/>
+      <c r="LH3" s="9"/>
+      <c r="LI3" s="9"/>
+      <c r="LJ3" s="9"/>
+      <c r="LK3" s="9"/>
+      <c r="LL3" s="9"/>
+      <c r="LM3" s="9"/>
+      <c r="LN3" s="9"/>
+      <c r="LO3" s="9"/>
+      <c r="LP3" s="9"/>
+      <c r="LQ3" s="9"/>
+      <c r="LR3" s="9"/>
+      <c r="LS3" s="9"/>
+      <c r="LT3" s="9"/>
+      <c r="LU3" s="9"/>
+      <c r="LV3" s="9"/>
+      <c r="LW3" s="9"/>
+      <c r="LX3" s="9"/>
+      <c r="LY3" s="9"/>
+      <c r="LZ3" s="9"/>
+      <c r="MA3" s="9"/>
+      <c r="MB3" s="9"/>
+      <c r="MC3" s="9"/>
+      <c r="MD3" s="9"/>
+      <c r="ME3" s="9"/>
+      <c r="MF3" s="9"/>
+      <c r="MG3" s="9"/>
+      <c r="MH3" s="9"/>
+      <c r="MI3" s="9"/>
+      <c r="MJ3" s="9"/>
+      <c r="MK3" s="9"/>
+      <c r="ML3" s="9"/>
+      <c r="MM3" s="9"/>
+      <c r="MN3" s="9"/>
+      <c r="MO3" s="9"/>
+      <c r="MP3" s="9"/>
+      <c r="MQ3" s="9"/>
+      <c r="MR3" s="9"/>
+      <c r="MS3" s="9"/>
+      <c r="MT3" s="9"/>
+      <c r="MU3" s="9"/>
+      <c r="MV3" s="9"/>
+      <c r="MW3" s="9"/>
+      <c r="MX3" s="9"/>
+      <c r="MY3" s="9"/>
+      <c r="MZ3" s="9"/>
+      <c r="NA3" s="9"/>
+      <c r="NB3" s="9"/>
+      <c r="NC3" s="9"/>
+      <c r="ND3" s="9"/>
+      <c r="NE3" s="9"/>
+      <c r="NF3" s="9"/>
+      <c r="NG3" s="9"/>
+      <c r="NH3" s="9"/>
+      <c r="NI3" s="9"/>
+      <c r="NJ3" s="9"/>
+      <c r="NK3" s="9"/>
+      <c r="NL3" s="9"/>
+      <c r="NM3" s="9"/>
+      <c r="NN3" s="9"/>
+      <c r="NO3" s="9"/>
+      <c r="NP3" s="9"/>
+      <c r="NQ3" s="9"/>
+      <c r="NR3" s="9"/>
+      <c r="NS3" s="9"/>
+      <c r="NT3" s="9"/>
+      <c r="NU3" s="9"/>
+      <c r="NV3" s="9"/>
+      <c r="NW3" s="9"/>
+      <c r="NX3" s="9"/>
+      <c r="NY3" s="9"/>
+      <c r="NZ3" s="9"/>
+      <c r="OA3" s="9"/>
+      <c r="OB3" s="9"/>
+      <c r="OC3" s="9"/>
+      <c r="OD3" s="9"/>
+      <c r="OE3" s="9"/>
+      <c r="OF3" s="9"/>
+      <c r="OG3" s="9"/>
+      <c r="OH3" s="9"/>
+      <c r="OI3" s="9"/>
+      <c r="OJ3" s="9"/>
+      <c r="OK3" s="9"/>
+      <c r="OL3" s="9"/>
+      <c r="OM3" s="9"/>
+      <c r="ON3" s="9"/>
+      <c r="OO3" s="9"/>
+      <c r="OP3" s="9"/>
+      <c r="OQ3" s="9"/>
+      <c r="OR3" s="9"/>
+      <c r="OS3" s="9"/>
+      <c r="OT3" s="9"/>
+      <c r="OU3" s="9"/>
+      <c r="OV3" s="9"/>
+      <c r="OW3" s="9"/>
+      <c r="OX3" s="9"/>
+      <c r="OY3" s="9"/>
+      <c r="OZ3" s="9"/>
+      <c r="PA3" s="9"/>
+      <c r="PB3" s="9"/>
+      <c r="PC3" s="9"/>
+      <c r="PD3" s="9"/>
+      <c r="PE3" s="9"/>
+      <c r="PF3" s="9"/>
+      <c r="PG3" s="9"/>
+      <c r="PH3" s="9"/>
+      <c r="PI3" s="9"/>
+      <c r="PJ3" s="9"/>
+      <c r="PK3" s="9"/>
+      <c r="PL3" s="9"/>
+      <c r="PM3" s="9"/>
+      <c r="PN3" s="9"/>
+      <c r="PO3" s="9"/>
+      <c r="PP3" s="9"/>
+      <c r="PQ3" s="9"/>
+      <c r="PR3" s="9"/>
+      <c r="PS3" s="9"/>
+      <c r="PT3" s="9"/>
+      <c r="PU3" s="9"/>
+      <c r="PV3" s="9"/>
+      <c r="PW3" s="9"/>
+      <c r="PX3" s="9"/>
+      <c r="PY3" s="9"/>
+      <c r="PZ3" s="9"/>
+      <c r="QA3" s="9"/>
+      <c r="QB3" s="9"/>
+      <c r="QC3" s="9"/>
+      <c r="QD3" s="9"/>
+      <c r="QE3" s="9"/>
+      <c r="QF3" s="9"/>
+      <c r="QG3" s="9"/>
+      <c r="QH3" s="9"/>
+      <c r="QI3" s="9"/>
+      <c r="QJ3" s="9"/>
+      <c r="QK3" s="9"/>
+      <c r="QL3" s="9"/>
+      <c r="QM3" s="9"/>
+      <c r="QN3" s="9"/>
+      <c r="QO3" s="9"/>
+      <c r="QP3" s="9"/>
+      <c r="QQ3" s="9"/>
+      <c r="QR3" s="9"/>
+      <c r="QS3" s="9"/>
+      <c r="QT3" s="9"/>
+      <c r="QU3" s="9"/>
+      <c r="QV3" s="9"/>
+      <c r="QW3" s="9"/>
+      <c r="QX3" s="9"/>
+      <c r="QY3" s="9"/>
+      <c r="QZ3" s="9"/>
+      <c r="RA3" s="9"/>
+      <c r="RB3" s="9"/>
+      <c r="RC3" s="9"/>
+      <c r="RD3" s="9"/>
+      <c r="RE3" s="9"/>
+      <c r="RF3" s="9"/>
+      <c r="RG3" s="9"/>
+      <c r="RH3" s="9"/>
+      <c r="RI3" s="9"/>
+      <c r="RJ3" s="9"/>
+      <c r="RK3" s="9"/>
+      <c r="RL3" s="9"/>
+      <c r="RM3" s="9"/>
+      <c r="RN3" s="9"/>
+      <c r="RO3" s="9"/>
+      <c r="RP3" s="9"/>
+      <c r="RQ3" s="9"/>
+      <c r="RR3" s="9"/>
+      <c r="RS3" s="9"/>
+      <c r="RT3" s="9"/>
+      <c r="RU3" s="9"/>
+      <c r="RV3" s="9"/>
+      <c r="RW3" s="9"/>
+      <c r="RX3" s="9"/>
+      <c r="RY3" s="9"/>
+      <c r="RZ3" s="9"/>
+      <c r="SA3" s="9"/>
+      <c r="SB3" s="9"/>
+      <c r="SC3" s="9"/>
+      <c r="SD3" s="9"/>
+      <c r="SE3" s="9"/>
+      <c r="SF3" s="9"/>
+    </row>
+    <row r="4" spans="1:500" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4">
+        <v>3125550188</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="F4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G4">
+        <v>60611</v>
+      </c>
+      <c r="H4" t="s">
+        <v>105</v>
+      </c>
+      <c r="I4" t="s">
+        <v>106</v>
+      </c>
+      <c r="J4" t="s">
+        <v>103</v>
+      </c>
+      <c r="K4" t="s">
+        <v>107</v>
+      </c>
+      <c r="L4">
+        <v>60661</v>
+      </c>
+      <c r="M4" t="s">
+        <v>105</v>
+      </c>
+      <c r="N4" t="s">
+        <v>106</v>
+      </c>
+      <c r="O4" t="s">
+        <v>103</v>
+      </c>
+      <c r="P4" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="9"/>
+      <c r="Z4" s="9"/>
+      <c r="AA4" s="9"/>
+      <c r="AB4" s="9"/>
+      <c r="AC4" s="9"/>
+      <c r="AD4" s="9"/>
+      <c r="AE4" s="9"/>
+      <c r="AF4" s="9"/>
+      <c r="AG4" s="9"/>
+      <c r="AH4" s="9"/>
+      <c r="AI4" s="9"/>
+      <c r="AJ4" s="9"/>
+      <c r="AK4" s="9"/>
+      <c r="AL4" s="9"/>
+      <c r="AM4" s="9"/>
+      <c r="AN4" s="9"/>
+      <c r="AO4" s="9"/>
+      <c r="AP4" s="9"/>
+      <c r="AQ4" s="9"/>
+      <c r="AR4" s="9"/>
+      <c r="AS4" s="9"/>
+      <c r="AT4" s="9"/>
+      <c r="AU4" s="9"/>
+      <c r="AV4" s="9"/>
+      <c r="AW4" s="9"/>
+      <c r="AX4" s="9"/>
+      <c r="AY4" s="9"/>
+      <c r="AZ4" s="9"/>
+      <c r="BA4" s="9"/>
+      <c r="BB4" s="9"/>
+      <c r="BC4" s="9"/>
+      <c r="BD4" s="9"/>
+      <c r="BE4" s="9"/>
+      <c r="BF4" s="9"/>
+      <c r="BG4" s="9"/>
+      <c r="BH4" s="9"/>
+      <c r="BI4" s="9"/>
+      <c r="BJ4" s="9"/>
+      <c r="BK4" s="9"/>
+      <c r="BL4" s="9"/>
+      <c r="BM4" s="9"/>
+      <c r="BN4" s="9"/>
+      <c r="BO4" s="9"/>
+      <c r="BP4" s="9"/>
+      <c r="BQ4" s="9"/>
+      <c r="BR4" s="9"/>
+      <c r="BS4" s="9"/>
+      <c r="BT4" s="9"/>
+      <c r="BU4" s="9"/>
+      <c r="BV4" s="9"/>
+      <c r="BW4" s="9"/>
+      <c r="BX4" s="9"/>
+      <c r="BY4" s="9"/>
+      <c r="BZ4" s="9"/>
+      <c r="CA4" s="9"/>
+      <c r="CB4" s="9"/>
+      <c r="CC4" s="9"/>
+      <c r="CD4" s="9"/>
+      <c r="CE4" s="9"/>
+      <c r="CF4" s="9"/>
+      <c r="CG4" s="9"/>
+      <c r="CH4" s="9"/>
+      <c r="CI4" s="9"/>
+      <c r="CJ4" s="9"/>
+      <c r="CK4" s="9"/>
+      <c r="CL4" s="9"/>
+      <c r="CM4" s="9"/>
+      <c r="CN4" s="9"/>
+      <c r="CO4" s="9"/>
+      <c r="CP4" s="9"/>
+      <c r="CQ4" s="9"/>
+      <c r="CR4" s="9"/>
+      <c r="CS4" s="9"/>
+      <c r="CT4" s="9"/>
+      <c r="CU4" s="9"/>
+      <c r="CV4" s="9"/>
+      <c r="CW4" s="9"/>
+      <c r="CX4" s="9"/>
+      <c r="CY4" s="9"/>
+      <c r="CZ4" s="9"/>
+      <c r="DA4" s="9"/>
+      <c r="DB4" s="9"/>
+      <c r="DC4" s="9"/>
+      <c r="DD4" s="9"/>
+      <c r="DE4" s="9"/>
+      <c r="DF4" s="9"/>
+      <c r="DG4" s="9"/>
+      <c r="DH4" s="9"/>
+      <c r="DI4" s="9"/>
+      <c r="DJ4" s="9"/>
+      <c r="DK4" s="9"/>
+      <c r="DL4" s="9"/>
+      <c r="DM4" s="9"/>
+      <c r="DN4" s="9"/>
+      <c r="DO4" s="9"/>
+      <c r="DP4" s="9"/>
+      <c r="DQ4" s="9"/>
+      <c r="DR4" s="9"/>
+      <c r="DS4" s="9"/>
+      <c r="DT4" s="9"/>
+      <c r="DU4" s="9"/>
+      <c r="DV4" s="9"/>
+      <c r="DW4" s="9"/>
+      <c r="DX4" s="9"/>
+      <c r="DY4" s="9"/>
+      <c r="DZ4" s="9"/>
+      <c r="EA4" s="9"/>
+      <c r="EB4" s="9"/>
+      <c r="EC4" s="9"/>
+      <c r="ED4" s="9"/>
+      <c r="EE4" s="9"/>
+      <c r="EF4" s="9"/>
+      <c r="EG4" s="9"/>
+      <c r="EH4" s="9"/>
+      <c r="EI4" s="9"/>
+      <c r="EJ4" s="9"/>
+      <c r="EK4" s="9"/>
+      <c r="EL4" s="9"/>
+      <c r="EM4" s="9"/>
+      <c r="EN4" s="9"/>
+      <c r="EO4" s="9"/>
+      <c r="EP4" s="9"/>
+      <c r="EQ4" s="9"/>
+      <c r="ER4" s="9"/>
+      <c r="ES4" s="9"/>
+      <c r="ET4" s="9"/>
+      <c r="EU4" s="9"/>
+      <c r="EV4" s="9"/>
+      <c r="EW4" s="9"/>
+      <c r="EX4" s="9"/>
+      <c r="EY4" s="9"/>
+      <c r="EZ4" s="9"/>
+      <c r="FA4" s="9"/>
+      <c r="FB4" s="9"/>
+      <c r="FC4" s="9"/>
+      <c r="FD4" s="9"/>
+      <c r="FE4" s="9"/>
+      <c r="FF4" s="9"/>
+      <c r="FG4" s="9"/>
+      <c r="FH4" s="9"/>
+      <c r="FI4" s="9"/>
+      <c r="FJ4" s="9"/>
+      <c r="FK4" s="9"/>
+      <c r="FL4" s="9"/>
+      <c r="FM4" s="9"/>
+      <c r="FN4" s="9"/>
+      <c r="FO4" s="9"/>
+      <c r="FP4" s="9"/>
+      <c r="FQ4" s="9"/>
+      <c r="FR4" s="9"/>
+      <c r="FS4" s="9"/>
+      <c r="FT4" s="9"/>
+      <c r="FU4" s="9"/>
+      <c r="FV4" s="9"/>
+      <c r="FW4" s="9"/>
+      <c r="FX4" s="9"/>
+      <c r="FY4" s="9"/>
+      <c r="FZ4" s="9"/>
+      <c r="GA4" s="9"/>
+      <c r="GB4" s="9"/>
+      <c r="GC4" s="9"/>
+      <c r="GD4" s="9"/>
+      <c r="GE4" s="9"/>
+      <c r="GF4" s="9"/>
+      <c r="GG4" s="9"/>
+      <c r="GH4" s="9"/>
+      <c r="GI4" s="9"/>
+      <c r="GJ4" s="9"/>
+      <c r="GK4" s="9"/>
+      <c r="GL4" s="9"/>
+      <c r="GM4" s="9"/>
+      <c r="GN4" s="9"/>
+      <c r="GO4" s="9"/>
+      <c r="GP4" s="9"/>
+      <c r="GQ4" s="9"/>
+      <c r="GR4" s="9"/>
+      <c r="GS4" s="9"/>
+      <c r="GT4" s="9"/>
+      <c r="GU4" s="9"/>
+      <c r="GV4" s="9"/>
+      <c r="GW4" s="9"/>
+      <c r="GX4" s="9"/>
+      <c r="GY4" s="9"/>
+      <c r="GZ4" s="9"/>
+      <c r="HA4" s="9"/>
+      <c r="HB4" s="9"/>
+      <c r="HC4" s="9"/>
+      <c r="HD4" s="9"/>
+      <c r="HE4" s="9"/>
+      <c r="HF4" s="9"/>
+      <c r="HG4" s="9"/>
+      <c r="HH4" s="9"/>
+      <c r="HI4" s="9"/>
+      <c r="HJ4" s="9"/>
+      <c r="HK4" s="9"/>
+      <c r="HL4" s="9"/>
+      <c r="HM4" s="9"/>
+      <c r="HN4" s="9"/>
+      <c r="HO4" s="9"/>
+      <c r="HP4" s="9"/>
+      <c r="HQ4" s="9"/>
+      <c r="HR4" s="9"/>
+      <c r="HS4" s="9"/>
+      <c r="HT4" s="9"/>
+      <c r="HU4" s="9"/>
+      <c r="HV4" s="9"/>
+      <c r="HW4" s="9"/>
+      <c r="HX4" s="9"/>
+      <c r="HY4" s="9"/>
+      <c r="HZ4" s="9"/>
+      <c r="IA4" s="9"/>
+      <c r="IB4" s="9"/>
+      <c r="IC4" s="9"/>
+      <c r="ID4" s="9"/>
+      <c r="IE4" s="9"/>
+      <c r="IF4" s="9"/>
+      <c r="IG4" s="9"/>
+      <c r="IH4" s="9"/>
+      <c r="II4" s="9"/>
+      <c r="IJ4" s="9"/>
+      <c r="IK4" s="9"/>
+      <c r="IL4" s="9"/>
+      <c r="IM4" s="9"/>
+      <c r="IN4" s="9"/>
+      <c r="IO4" s="9"/>
+      <c r="IP4" s="9"/>
+      <c r="IQ4" s="9"/>
+      <c r="IR4" s="9"/>
+      <c r="IS4" s="9"/>
+      <c r="IT4" s="9"/>
+      <c r="IU4" s="9"/>
+      <c r="IV4" s="9"/>
+      <c r="IW4" s="9"/>
+      <c r="IX4" s="9"/>
+      <c r="IY4" s="9"/>
+      <c r="IZ4" s="9"/>
+      <c r="JA4" s="9"/>
+      <c r="JB4" s="9"/>
+      <c r="JC4" s="9"/>
+      <c r="JD4" s="9"/>
+      <c r="JE4" s="9"/>
+      <c r="JF4" s="9"/>
+      <c r="JG4" s="9"/>
+      <c r="JH4" s="9"/>
+      <c r="JI4" s="9"/>
+      <c r="JJ4" s="9"/>
+      <c r="JK4" s="9"/>
+      <c r="JL4" s="9"/>
+      <c r="JM4" s="9"/>
+      <c r="JN4" s="9"/>
+      <c r="JO4" s="9"/>
+      <c r="JP4" s="9"/>
+      <c r="JQ4" s="9"/>
+      <c r="JR4" s="9"/>
+      <c r="JS4" s="9"/>
+      <c r="JT4" s="9"/>
+      <c r="JU4" s="9"/>
+      <c r="JV4" s="9"/>
+      <c r="JW4" s="9"/>
+      <c r="JX4" s="9"/>
+      <c r="JY4" s="9"/>
+      <c r="JZ4" s="9"/>
+      <c r="KA4" s="9"/>
+      <c r="KB4" s="9"/>
+      <c r="KC4" s="9"/>
+      <c r="KD4" s="9"/>
+      <c r="KE4" s="9"/>
+      <c r="KF4" s="9"/>
+      <c r="KG4" s="9"/>
+      <c r="KH4" s="9"/>
+      <c r="KI4" s="9"/>
+      <c r="KJ4" s="9"/>
+      <c r="KK4" s="9"/>
+      <c r="KL4" s="9"/>
+      <c r="KM4" s="9"/>
+      <c r="KN4" s="9"/>
+      <c r="KO4" s="9"/>
+      <c r="KP4" s="9"/>
+      <c r="KQ4" s="9"/>
+      <c r="KR4" s="9"/>
+      <c r="KS4" s="9"/>
+      <c r="KT4" s="9"/>
+      <c r="KU4" s="9"/>
+      <c r="KV4" s="9"/>
+      <c r="KW4" s="9"/>
+      <c r="KX4" s="9"/>
+      <c r="KY4" s="9"/>
+      <c r="KZ4" s="9"/>
+      <c r="LA4" s="9"/>
+      <c r="LB4" s="9"/>
+      <c r="LC4" s="9"/>
+      <c r="LD4" s="9"/>
+      <c r="LE4" s="9"/>
+      <c r="LF4" s="9"/>
+      <c r="LG4" s="9"/>
+      <c r="LH4" s="9"/>
+      <c r="LI4" s="9"/>
+      <c r="LJ4" s="9"/>
+      <c r="LK4" s="9"/>
+      <c r="LL4" s="9"/>
+      <c r="LM4" s="9"/>
+      <c r="LN4" s="9"/>
+      <c r="LO4" s="9"/>
+      <c r="LP4" s="9"/>
+      <c r="LQ4" s="9"/>
+      <c r="LR4" s="9"/>
+      <c r="LS4" s="9"/>
+      <c r="LT4" s="9"/>
+      <c r="LU4" s="9"/>
+      <c r="LV4" s="9"/>
+      <c r="LW4" s="9"/>
+      <c r="LX4" s="9"/>
+      <c r="LY4" s="9"/>
+      <c r="LZ4" s="9"/>
+      <c r="MA4" s="9"/>
+      <c r="MB4" s="9"/>
+      <c r="MC4" s="9"/>
+      <c r="MD4" s="9"/>
+      <c r="ME4" s="9"/>
+      <c r="MF4" s="9"/>
+      <c r="MG4" s="9"/>
+      <c r="MH4" s="9"/>
+      <c r="MI4" s="9"/>
+      <c r="MJ4" s="9"/>
+      <c r="MK4" s="9"/>
+      <c r="ML4" s="9"/>
+      <c r="MM4" s="9"/>
+      <c r="MN4" s="9"/>
+      <c r="MO4" s="9"/>
+      <c r="MP4" s="9"/>
+      <c r="MQ4" s="9"/>
+      <c r="MR4" s="9"/>
+      <c r="MS4" s="9"/>
+      <c r="MT4" s="9"/>
+      <c r="MU4" s="9"/>
+      <c r="MV4" s="9"/>
+      <c r="MW4" s="9"/>
+      <c r="MX4" s="9"/>
+      <c r="MY4" s="9"/>
+      <c r="MZ4" s="9"/>
+      <c r="NA4" s="9"/>
+      <c r="NB4" s="9"/>
+      <c r="NC4" s="9"/>
+      <c r="ND4" s="9"/>
+      <c r="NE4" s="9"/>
+      <c r="NF4" s="9"/>
+      <c r="NG4" s="9"/>
+      <c r="NH4" s="9"/>
+      <c r="NI4" s="9"/>
+      <c r="NJ4" s="9"/>
+      <c r="NK4" s="9"/>
+      <c r="NL4" s="9"/>
+      <c r="NM4" s="9"/>
+      <c r="NN4" s="9"/>
+      <c r="NO4" s="9"/>
+      <c r="NP4" s="9"/>
+      <c r="NQ4" s="9"/>
+      <c r="NR4" s="9"/>
+      <c r="NS4" s="9"/>
+      <c r="NT4" s="9"/>
+      <c r="NU4" s="9"/>
+      <c r="NV4" s="9"/>
+      <c r="NW4" s="9"/>
+      <c r="NX4" s="9"/>
+      <c r="NY4" s="9"/>
+      <c r="NZ4" s="9"/>
+      <c r="OA4" s="9"/>
+      <c r="OB4" s="9"/>
+      <c r="OC4" s="9"/>
+      <c r="OD4" s="9"/>
+      <c r="OE4" s="9"/>
+      <c r="OF4" s="9"/>
+      <c r="OG4" s="9"/>
+      <c r="OH4" s="9"/>
+      <c r="OI4" s="9"/>
+      <c r="OJ4" s="9"/>
+      <c r="OK4" s="9"/>
+      <c r="OL4" s="9"/>
+      <c r="OM4" s="9"/>
+      <c r="ON4" s="9"/>
+      <c r="OO4" s="9"/>
+      <c r="OP4" s="9"/>
+      <c r="OQ4" s="9"/>
+      <c r="OR4" s="9"/>
+      <c r="OS4" s="9"/>
+      <c r="OT4" s="9"/>
+      <c r="OU4" s="9"/>
+      <c r="OV4" s="9"/>
+      <c r="OW4" s="9"/>
+      <c r="OX4" s="9"/>
+      <c r="OY4" s="9"/>
+      <c r="OZ4" s="9"/>
+      <c r="PA4" s="9"/>
+      <c r="PB4" s="9"/>
+      <c r="PC4" s="9"/>
+      <c r="PD4" s="9"/>
+      <c r="PE4" s="9"/>
+      <c r="PF4" s="9"/>
+      <c r="PG4" s="9"/>
+      <c r="PH4" s="9"/>
+      <c r="PI4" s="9"/>
+      <c r="PJ4" s="9"/>
+      <c r="PK4" s="9"/>
+      <c r="PL4" s="9"/>
+      <c r="PM4" s="9"/>
+      <c r="PN4" s="9"/>
+      <c r="PO4" s="9"/>
+      <c r="PP4" s="9"/>
+      <c r="PQ4" s="9"/>
+      <c r="PR4" s="9"/>
+      <c r="PS4" s="9"/>
+      <c r="PT4" s="9"/>
+      <c r="PU4" s="9"/>
+      <c r="PV4" s="9"/>
+      <c r="PW4" s="9"/>
+      <c r="PX4" s="9"/>
+      <c r="PY4" s="9"/>
+      <c r="PZ4" s="9"/>
+      <c r="QA4" s="9"/>
+      <c r="QB4" s="9"/>
+      <c r="QC4" s="9"/>
+      <c r="QD4" s="9"/>
+      <c r="QE4" s="9"/>
+      <c r="QF4" s="9"/>
+      <c r="QG4" s="9"/>
+      <c r="QH4" s="9"/>
+      <c r="QI4" s="9"/>
+      <c r="QJ4" s="9"/>
+      <c r="QK4" s="9"/>
+      <c r="QL4" s="9"/>
+      <c r="QM4" s="9"/>
+      <c r="QN4" s="9"/>
+      <c r="QO4" s="9"/>
+      <c r="QP4" s="9"/>
+      <c r="QQ4" s="9"/>
+      <c r="QR4" s="9"/>
+      <c r="QS4" s="9"/>
+      <c r="QT4" s="9"/>
+      <c r="QU4" s="9"/>
+      <c r="QV4" s="9"/>
+      <c r="QW4" s="9"/>
+      <c r="QX4" s="9"/>
+      <c r="QY4" s="9"/>
+      <c r="QZ4" s="9"/>
+      <c r="RA4" s="9"/>
+      <c r="RB4" s="9"/>
+      <c r="RC4" s="9"/>
+      <c r="RD4" s="9"/>
+      <c r="RE4" s="9"/>
+      <c r="RF4" s="9"/>
+      <c r="RG4" s="9"/>
+      <c r="RH4" s="9"/>
+      <c r="RI4" s="9"/>
+      <c r="RJ4" s="9"/>
+      <c r="RK4" s="9"/>
+      <c r="RL4" s="9"/>
+      <c r="RM4" s="9"/>
+      <c r="RN4" s="9"/>
+      <c r="RO4" s="9"/>
+      <c r="RP4" s="9"/>
+      <c r="RQ4" s="9"/>
+      <c r="RR4" s="9"/>
+      <c r="RS4" s="9"/>
+      <c r="RT4" s="9"/>
+      <c r="RU4" s="9"/>
+      <c r="RV4" s="9"/>
+      <c r="RW4" s="9"/>
+      <c r="RX4" s="9"/>
+      <c r="RY4" s="9"/>
+      <c r="RZ4" s="9"/>
+      <c r="SA4" s="9"/>
+      <c r="SB4" s="9"/>
+      <c r="SC4" s="9"/>
+      <c r="SD4" s="9"/>
+      <c r="SE4" s="9"/>
+      <c r="SF4" s="9"/>
+    </row>
+    <row r="5" spans="1:500" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="D5">
+        <v>3055550145</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="F5" t="s">
+        <v>112</v>
+      </c>
+      <c r="G5">
+        <v>33132</v>
+      </c>
+      <c r="H5" t="s">
+        <v>113</v>
+      </c>
+      <c r="I5" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" t="s">
+        <v>103</v>
+      </c>
+      <c r="K5" t="s">
+        <v>114</v>
+      </c>
+      <c r="L5">
+        <v>33131</v>
+      </c>
+      <c r="M5" t="s">
+        <v>113</v>
+      </c>
+      <c r="N5" t="s">
+        <v>60</v>
+      </c>
+      <c r="O5" t="s">
+        <v>103</v>
+      </c>
+      <c r="P5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:500" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D6">
+        <v>2145550167</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="F6" t="s">
+        <v>120</v>
+      </c>
+      <c r="G6">
+        <v>75201</v>
+      </c>
+      <c r="H6" t="s">
+        <v>121</v>
+      </c>
+      <c r="I6" t="s">
+        <v>56</v>
+      </c>
+      <c r="J6" t="s">
+        <v>103</v>
+      </c>
+      <c r="K6" t="s">
+        <v>122</v>
+      </c>
+      <c r="L6">
+        <v>75201</v>
+      </c>
+      <c r="M6" t="s">
+        <v>121</v>
+      </c>
+      <c r="N6" t="s">
+        <v>56</v>
+      </c>
+      <c r="O6" t="s">
+        <v>103</v>
+      </c>
+      <c r="P6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:500" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D7">
+        <v>2065550189</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="F7" t="s">
+        <v>128</v>
+      </c>
+      <c r="G7">
+        <v>98101</v>
+      </c>
+      <c r="H7" t="s">
+        <v>129</v>
+      </c>
+      <c r="I7" t="s">
+        <v>130</v>
+      </c>
+      <c r="J7" t="s">
+        <v>103</v>
+      </c>
+      <c r="K7" t="s">
+        <v>131</v>
+      </c>
+      <c r="L7">
+        <v>98101</v>
+      </c>
+      <c r="M7" t="s">
+        <v>129</v>
+      </c>
+      <c r="N7" t="s">
+        <v>130</v>
+      </c>
+      <c r="O7" t="s">
+        <v>103</v>
+      </c>
+      <c r="P7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="8" spans="1:500" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="D8">
+        <v>3035550134</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F8" t="s">
+        <v>137</v>
+      </c>
+      <c r="G8">
+        <v>80202</v>
+      </c>
+      <c r="H8" t="s">
+        <v>138</v>
+      </c>
+      <c r="I8" t="s">
+        <v>139</v>
+      </c>
+      <c r="J8" t="s">
+        <v>103</v>
+      </c>
+      <c r="K8" t="s">
+        <v>140</v>
+      </c>
+      <c r="L8">
+        <v>80203</v>
+      </c>
+      <c r="M8" t="s">
+        <v>138</v>
+      </c>
+      <c r="N8" t="s">
+        <v>139</v>
+      </c>
+      <c r="O8" t="s">
+        <v>103</v>
+      </c>
+      <c r="P8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="9" spans="1:500" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>142</v>
+      </c>
+      <c r="B9" t="s">
+        <v>143</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D9">
+        <v>4085550156</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="F9" t="s">
+        <v>146</v>
+      </c>
+      <c r="G9">
+        <v>95002</v>
+      </c>
+      <c r="H9" t="s">
+        <v>147</v>
+      </c>
+      <c r="I9" t="s">
+        <v>109</v>
+      </c>
+      <c r="J9" t="s">
+        <v>103</v>
+      </c>
+      <c r="K9" t="s">
+        <v>148</v>
+      </c>
+      <c r="L9">
+        <v>95110</v>
+      </c>
+      <c r="M9" t="s">
+        <v>147</v>
+      </c>
+      <c r="N9" t="s">
+        <v>109</v>
+      </c>
+      <c r="O9" t="s">
+        <v>103</v>
+      </c>
+      <c r="P9" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="10" spans="1:500" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>150</v>
+      </c>
+      <c r="B10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D10">
+        <v>6175550178</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="F10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G10">
+        <v>2116</v>
+      </c>
+      <c r="H10" t="s">
+        <v>155</v>
+      </c>
+      <c r="I10" t="s">
+        <v>156</v>
+      </c>
+      <c r="J10" t="s">
+        <v>103</v>
+      </c>
+      <c r="K10" t="s">
+        <v>157</v>
+      </c>
+      <c r="L10">
+        <v>2110</v>
+      </c>
+      <c r="M10" t="s">
+        <v>155</v>
+      </c>
+      <c r="N10" t="s">
+        <v>156</v>
+      </c>
+      <c r="O10" t="s">
+        <v>103</v>
+      </c>
+      <c r="P10" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="11" spans="1:500" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>159</v>
+      </c>
+      <c r="B11" t="s">
+        <v>160</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="D11">
+        <v>4045550190</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="F11" t="s">
+        <v>163</v>
+      </c>
+      <c r="G11">
+        <v>30303</v>
+      </c>
+      <c r="H11" t="s">
+        <v>164</v>
+      </c>
+      <c r="I11" t="s">
+        <v>165</v>
+      </c>
+      <c r="J11" t="s">
+        <v>103</v>
+      </c>
+      <c r="K11" t="s">
+        <v>166</v>
+      </c>
+      <c r="L11">
+        <v>30303</v>
+      </c>
+      <c r="M11" t="s">
+        <v>164</v>
+      </c>
+      <c r="N11" t="s">
+        <v>165</v>
+      </c>
+      <c r="O11" t="s">
+        <v>103</v>
+      </c>
+      <c r="P11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="12" spans="1:500" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>168</v>
+      </c>
+      <c r="B12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="D12">
+        <v>5035550128</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="F12" t="s">
+        <v>172</v>
+      </c>
+      <c r="G12">
+        <v>97204</v>
+      </c>
+      <c r="H12" t="s">
+        <v>173</v>
+      </c>
+      <c r="I12" t="s">
+        <v>174</v>
+      </c>
+      <c r="J12" t="s">
+        <v>103</v>
+      </c>
+      <c r="K12" t="s">
+        <v>175</v>
+      </c>
+      <c r="L12">
+        <v>97209</v>
+      </c>
+      <c r="M12" t="s">
+        <v>173</v>
+      </c>
+      <c r="N12" t="s">
+        <v>174</v>
+      </c>
+      <c r="O12" t="s">
+        <v>103</v>
+      </c>
+      <c r="P12" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13" spans="1:500" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>177</v>
+      </c>
+      <c r="B13" t="s">
+        <v>178</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D13">
+        <v>2025550140</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="F13" t="s">
+        <v>181</v>
+      </c>
+      <c r="G13">
+        <v>20005</v>
+      </c>
+      <c r="H13" t="s">
+        <v>130</v>
+      </c>
+      <c r="I13" t="s">
+        <v>182</v>
+      </c>
+      <c r="J13" t="s">
+        <v>103</v>
+      </c>
+      <c r="K13" t="s">
+        <v>183</v>
+      </c>
+      <c r="L13">
+        <v>20006</v>
+      </c>
+      <c r="M13" t="s">
+        <v>130</v>
+      </c>
+      <c r="N13" t="s">
+        <v>182</v>
+      </c>
+      <c r="O13" t="s">
+        <v>103</v>
+      </c>
+      <c r="P13" t="s">
+        <v>184</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" display="https://www.acmesolutions.com/" xr:uid="{91C5AE5D-CB99-414B-89FF-0DF7447A17A4}"/>
+    <hyperlink ref="E2" r:id="rId2" display="mailto:contact@acmesolutions.com" xr:uid="{A21753E9-12B7-4D47-AAEA-605825E25038}"/>
+    <hyperlink ref="C3" r:id="rId3" display="https://www.globaltechservices.com/" xr:uid="{8730483A-8934-4146-92C5-37BA72D326F7}"/>
+    <hyperlink ref="E3" r:id="rId4" display="mailto:info@globaltechservices.com" xr:uid="{D36A8F55-E723-9A40-A24E-340AD89F484D}"/>
+    <hyperlink ref="C5" r:id="rId5" display="https://www.bluehorizon.example/" xr:uid="{E118D4DE-06B6-AF43-821F-E0EB37BAB73E}"/>
+    <hyperlink ref="E5" r:id="rId6" display="mailto:contact@bluehorizon.example" xr:uid="{4C32D9FC-77A3-AF4C-970C-8BD5A4ABC668}"/>
+    <hyperlink ref="C6" r:id="rId7" display="https://www.silveroak.example/" xr:uid="{8A351257-1513-8849-A41B-0F376F5C4A38}"/>
+    <hyperlink ref="E6" r:id="rId8" display="mailto:sales@silveroak.example" xr:uid="{8042B489-6B38-4740-AD74-D6538F6E7C7A}"/>
+    <hyperlink ref="C7" r:id="rId9" display="https://www.greenvalley.example/" xr:uid="{416745D9-AA77-FA4C-8D72-1452504FCCD9}"/>
+    <hyperlink ref="E7" r:id="rId10" display="mailto:orders@greenvalley.example" xr:uid="{FF194C1D-2CB7-2046-BC72-E2F8CF9E50EA}"/>
+    <hyperlink ref="C8" r:id="rId11" display="https://www.summitpeak.example/" xr:uid="{F83393D1-EC3C-234A-B955-97228E396772}"/>
+    <hyperlink ref="E8" r:id="rId12" display="mailto:support@summitpeak.example" xr:uid="{1DE78D4B-F4FF-974F-B217-BAFE491A1AAB}"/>
+    <hyperlink ref="C9" r:id="rId13" display="https://www.goldengate.example/" xr:uid="{63CC1111-693E-A744-99CA-01E1C56D8CF3}"/>
+    <hyperlink ref="E9" r:id="rId14" display="mailto:logistics@goldengate.example" xr:uid="{E84587CC-1295-3348-B049-9BFBABDCFBF2}"/>
+    <hyperlink ref="C10" r:id="rId15" display="https://www.libertyfinancial.example/" xr:uid="{88815617-16D7-C94E-98F9-344B093253E8}"/>
+    <hyperlink ref="E10" r:id="rId16" display="mailto:finance@libertyfinancial.example" xr:uid="{2458E717-89A8-114F-9DE7-797DF718497E}"/>
+    <hyperlink ref="C11" r:id="rId17" display="https://www.riverstone.example/" xr:uid="{5C1FFC04-11A5-D64D-BE1A-C76CE45BF5CB}"/>
+    <hyperlink ref="E11" r:id="rId18" display="mailto:contact@riverstone.example" xr:uid="{13237086-9429-0948-AC42-C1BF6A2C37F7}"/>
+    <hyperlink ref="C12" r:id="rId19" display="https://www.pacificedge.example/" xr:uid="{8FE4F6FF-03E9-5F44-9465-48C98001A6EE}"/>
+    <hyperlink ref="E12" r:id="rId20" display="mailto:sales@pacificedge.example" xr:uid="{8A87332A-69D4-064B-9FFC-D8FFD571AB6A}"/>
+    <hyperlink ref="C13" r:id="rId21" display="https://www.capitalbridge.example/" xr:uid="{6C55603C-C00F-FA49-8692-B99C02AB7669}"/>
+    <hyperlink ref="E13" r:id="rId22" display="mailto:info@capitalbridge.example" xr:uid="{BD92F6E6-A1E1-E742-B203-317AB189872E}"/>
+    <hyperlink ref="C4" r:id="rId23" display="https://www.globaltechservices.com/" xr:uid="{7B81556A-DDD4-6048-A6EE-9AC0CEE05FC7}"/>
+    <hyperlink ref="E4" r:id="rId24" display="mailto:info@globaltechservices.com" xr:uid="{87B0A03E-1851-C44A-A08A-E4D868C0E9A0}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01E85675-CCBB-4BF0-940B-9BD2D2BEEE01}">
+  <dimension ref="A1:U2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="6">
+        <v>47026</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/testData/testData.xlsx
+++ b/testData/testData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manga\PW1_Titans\Playwright_Titans\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{149CB0A3-319D-4906-A129-6365F197BDC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A346FAD-543C-4627-9D97-66B82027BA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10800" yWindow="210" windowWidth="15795" windowHeight="15030" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="login" sheetId="1" r:id="rId1"/>
@@ -19,10 +19,21 @@
     <sheet name="meetings" sheetId="4" r:id="rId4"/>
     <sheet name="Quotes" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -32,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="98">
   <si>
     <t>testCase</t>
   </si>
@@ -298,15 +309,6 @@
     <t>Test lead for Robert Smith</t>
   </si>
   <si>
-    <t>Subject</t>
-  </si>
-  <si>
-    <t>CreateMeeting</t>
-  </si>
-  <si>
-    <t>Contract renewal1</t>
-  </si>
-  <si>
     <t>Title</t>
   </si>
   <si>
@@ -323,6 +325,18 @@
   </si>
   <si>
     <t>On Hold</t>
+  </si>
+  <si>
+    <t>Initial meeting</t>
+  </si>
+  <si>
+    <t>startDate</t>
+  </si>
+  <si>
+    <t>TC001</t>
+  </si>
+  <si>
+    <t>subject</t>
   </si>
 </sst>
 </file>
@@ -738,7 +752,7 @@
     <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -832,6 +846,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB7CBB58-CC32-3442-AC7F-92AB77965A23}">
   <dimension ref="A1:V4"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="31.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
@@ -1112,27 +1149,35 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A1278E-4E8F-4C4D-B5F7-52E9C6CC17A7}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.85546875" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+      <c r="C1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>94</v>
+      </c>
+      <c r="C2" t="str">
+        <f ca="1">TEXT(TODAY()-1,"yyyy-mm-dd")</f>
+        <v>2026-10-04</v>
       </c>
     </row>
   </sheetData>
@@ -1156,24 +1201,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D2">
         <v>30</v>

--- a/testData/testData.xlsx
+++ b/testData/testData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manga\PW1_Titans\Playwright_Titans\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A346FAD-543C-4627-9D97-66B82027BA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E831B8F-91D9-45BB-B457-071F03CFED47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="login" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="100">
   <si>
     <t>testCase</t>
   </si>
@@ -327,9 +327,6 @@
     <t>On Hold</t>
   </si>
   <si>
-    <t>Initial meeting</t>
-  </si>
-  <si>
     <t>startDate</t>
   </si>
   <si>
@@ -337,6 +334,15 @@
   </si>
   <si>
     <t>subject</t>
+  </si>
+  <si>
+    <t>TC002</t>
+  </si>
+  <si>
+    <t>Final negotiation</t>
+  </si>
+  <si>
+    <t>Contract final discussions</t>
   </si>
 </sst>
 </file>
@@ -1149,11 +1155,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A1278E-4E8F-4C4D-B5F7-52E9C6CC17A7}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1162,22 +1168,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C2" t="str">
-        <f ca="1">TEXT(TODAY()-1,"yyyy-mm-dd")</f>
-        <v>2026-10-04</v>
+        <f ca="1">TEXT(TODAY(),"yyyy-mm-dd")</f>
+        <v>2026-10-05</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" t="str">
+        <f ca="1">TEXT(TODAY()-3,"yyyy-mm-dd")</f>
+        <v>2026-10-02</v>
       </c>
     </row>
   </sheetData>
